--- a/server/data/gnta-visitors-quarterly.xlsx
+++ b/server/data/gnta-visitors-quarterly.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a.arabuli\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA2A793-35C0-4605-BE5E-21AC1A3B43EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B6DBBF-024C-4D99-B357-213F2DDCC0B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="746" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2026" sheetId="1" r:id="rId1"/>
+    <sheet name="2026 II კვარტალი" sheetId="1" r:id="rId1"/>
     <sheet name="ტოპ 15" sheetId="2" r:id="rId2"/>
     <sheet name="ვიზიტის ტიპები" sheetId="12" r:id="rId3"/>
     <sheet name="რეგიონები" sheetId="3" r:id="rId4"/>
@@ -993,12 +993,6 @@
     <t>ევროკავშირის ქვეყნები და  გაერთიანებული სამეფო</t>
   </si>
   <si>
-    <t>2025 I კვ</t>
-  </si>
-  <si>
-    <t>2026 I კვ</t>
-  </si>
-  <si>
     <t>ცვლილება 2025/2026</t>
   </si>
   <si>
@@ -1015,6 +1009,12 @@
   </si>
   <si>
     <t>ჩრდილოეთ მაკედონიის რესპუბლიკა</t>
+  </si>
+  <si>
+    <t>2025 II კვ</t>
+  </si>
+  <si>
+    <t>2026 II კვ</t>
   </si>
   <si>
     <t>აშშ</t>
@@ -2033,7 +2033,7 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="171">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2487,6 +2487,12 @@
     </xf>
     <xf numFmtId="3" fontId="13" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3175,7 +3181,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G241"/>
+  <dimension ref="A1:J241"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="5" customWidth="1"/>
@@ -3192,16 +3198,16 @@
         <v>0</v>
       </c>
       <c r="C1" s="43" t="s">
+        <v>294</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>295</v>
+      </c>
+      <c r="E1" s="43" t="s">
         <v>288</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="F1" s="92" t="s">
         <v>289</v>
-      </c>
-      <c r="E1" s="43" t="s">
-        <v>290</v>
-      </c>
-      <c r="F1" s="92" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="2" spans="2:7" s="20" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3209,18 +3215,18 @@
         <v>248</v>
       </c>
       <c r="C2" s="57">
-        <v>1314828</v>
+        <v>1838913</v>
       </c>
       <c r="D2" s="57">
-        <v>1300505</v>
+        <v>1749668</v>
       </c>
       <c r="E2" s="57">
         <f>D2-C2</f>
-        <v>-14323</v>
+        <v>-89245</v>
       </c>
       <c r="F2" s="117">
         <f>D2/C2-1</f>
-        <v>-1.0893440054516645E-2</v>
+        <v>-4.8531387836183604E-2</v>
       </c>
     </row>
     <row r="3" spans="2:7" s="20" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3228,18 +3234,18 @@
         <v>237</v>
       </c>
       <c r="C3" s="58">
-        <v>142492</v>
+        <v>200725</v>
       </c>
       <c r="D3" s="58">
-        <v>130143</v>
+        <v>185526</v>
       </c>
       <c r="E3" s="58">
         <f>D3-C3</f>
-        <v>-12349</v>
+        <v>-15199</v>
       </c>
       <c r="F3" s="118">
         <f>D3/C3-1</f>
-        <v>-8.6664514499059542E-2</v>
+        <v>-7.572051313986794E-2</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3247,18 +3253,18 @@
         <v>249</v>
       </c>
       <c r="C4" s="48">
-        <v>1172336</v>
+        <v>1638188</v>
       </c>
       <c r="D4" s="48">
-        <v>1170362</v>
+        <v>1564142</v>
       </c>
       <c r="E4" s="48">
         <f>D4-C4</f>
-        <v>-1974</v>
+        <v>-74046</v>
       </c>
       <c r="F4" s="119">
         <f>D4/C4-1</f>
-        <v>-1.6838176086036993E-3</v>
+        <v>-4.5199940421978391E-2</v>
       </c>
     </row>
     <row r="5" spans="2:7" s="20" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3276,18 +3282,18 @@
         <v>1</v>
       </c>
       <c r="C6" s="49">
-        <v>933040</v>
+        <v>1310994</v>
       </c>
       <c r="D6" s="50">
-        <v>946150</v>
+        <v>1330596</v>
       </c>
       <c r="E6" s="49">
         <f>D6-C6</f>
-        <v>13110</v>
+        <v>19602</v>
       </c>
       <c r="F6" s="142">
         <f>D6/C6-1</f>
-        <v>1.4050844551144692E-2</v>
+        <v>1.4952013510359352E-2</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
@@ -3295,18 +3301,18 @@
         <v>2</v>
       </c>
       <c r="C7" s="52">
-        <v>575892</v>
+        <v>825526</v>
       </c>
       <c r="D7" s="52">
-        <v>572362</v>
+        <v>857386</v>
       </c>
       <c r="E7" s="52">
         <f t="shared" ref="E7:E67" si="0">D7-C7</f>
-        <v>-3530</v>
+        <v>31860</v>
       </c>
       <c r="F7" s="143">
         <f t="shared" ref="F7:F67" si="1">D7/C7-1</f>
-        <v>-6.1296215262583997E-3</v>
+        <v>3.8593575490051268E-2</v>
       </c>
     </row>
     <row r="8" spans="2:7" s="13" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3314,18 +3320,18 @@
         <v>4</v>
       </c>
       <c r="C8" s="38">
-        <v>64818</v>
+        <v>70430</v>
       </c>
       <c r="D8" s="38">
-        <v>59571</v>
+        <v>73774</v>
       </c>
       <c r="E8" s="38">
         <f t="shared" si="0"/>
-        <v>-5247</v>
+        <v>3344</v>
       </c>
       <c r="F8" s="144">
         <f t="shared" si="1"/>
-        <v>-8.0949736184393273E-2</v>
+        <v>4.7479767144682716E-2</v>
       </c>
     </row>
     <row r="9" spans="2:7" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
@@ -3333,18 +3339,18 @@
         <v>5</v>
       </c>
       <c r="C9" s="38">
-        <v>17377</v>
+        <v>28871</v>
       </c>
       <c r="D9" s="38">
-        <v>16904</v>
+        <v>29316</v>
       </c>
       <c r="E9" s="38">
         <f t="shared" si="0"/>
-        <v>-473</v>
+        <v>445</v>
       </c>
       <c r="F9" s="144">
         <f t="shared" si="1"/>
-        <v>-2.7219888358174571E-2</v>
+        <v>1.5413390599563481E-2</v>
       </c>
     </row>
     <row r="10" spans="2:7" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
@@ -3352,18 +3358,18 @@
         <v>6</v>
       </c>
       <c r="C10" s="38">
-        <v>1837</v>
+        <v>2674</v>
       </c>
       <c r="D10" s="38">
-        <v>2136</v>
+        <v>3087</v>
       </c>
       <c r="E10" s="38">
         <f t="shared" si="0"/>
-        <v>299</v>
+        <v>413</v>
       </c>
       <c r="F10" s="144">
         <f t="shared" si="1"/>
-        <v>0.16276537833424065</v>
+        <v>0.15445026178010468</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3371,18 +3377,18 @@
         <v>8</v>
       </c>
       <c r="C11" s="38">
-        <v>1332</v>
+        <v>1708</v>
       </c>
       <c r="D11" s="38">
-        <v>1138</v>
+        <v>1698</v>
       </c>
       <c r="E11" s="38">
         <f t="shared" si="0"/>
-        <v>-194</v>
+        <v>-10</v>
       </c>
       <c r="F11" s="144">
         <f t="shared" si="1"/>
-        <v>-0.14564564564564564</v>
+        <v>-5.8548009367681564E-3</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3390,18 +3396,18 @@
         <v>19</v>
       </c>
       <c r="C12" s="38">
-        <v>4263</v>
+        <v>4303</v>
       </c>
       <c r="D12" s="38">
-        <v>4397</v>
+        <v>4375</v>
       </c>
       <c r="E12" s="38">
         <f t="shared" si="0"/>
-        <v>134</v>
+        <v>72</v>
       </c>
       <c r="F12" s="144">
         <f t="shared" si="1"/>
-        <v>3.1433262960356645E-2</v>
+        <v>1.6732512200790195E-2</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3409,37 +3415,37 @@
         <v>12</v>
       </c>
       <c r="C13" s="38">
-        <v>3375</v>
+        <v>4671</v>
       </c>
       <c r="D13" s="38">
-        <v>2508</v>
+        <v>5337</v>
       </c>
       <c r="E13" s="38">
         <f t="shared" si="0"/>
-        <v>-867</v>
+        <v>666</v>
       </c>
       <c r="F13" s="144">
         <f t="shared" si="1"/>
-        <v>-0.25688888888888894</v>
+        <v>0.1425818882466281</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="82" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C14" s="38">
-        <v>3441</v>
+        <v>4679</v>
       </c>
       <c r="D14" s="38">
-        <v>4470</v>
+        <v>6324</v>
       </c>
       <c r="E14" s="38">
         <f t="shared" si="0"/>
-        <v>1029</v>
+        <v>1645</v>
       </c>
       <c r="F14" s="144">
         <f t="shared" si="1"/>
-        <v>0.29904097646033123</v>
+        <v>0.35157084847189579</v>
       </c>
     </row>
     <row r="15" spans="2:7" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3447,18 +3453,18 @@
         <v>13</v>
       </c>
       <c r="C15" s="38">
-        <v>2717</v>
+        <v>3342</v>
       </c>
       <c r="D15" s="38">
-        <v>3003</v>
+        <v>3610</v>
       </c>
       <c r="E15" s="38">
         <f t="shared" si="0"/>
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="F15" s="144">
         <f t="shared" si="1"/>
-        <v>0.10526315789473695</v>
+        <v>8.0191502094554057E-2</v>
       </c>
     </row>
     <row r="16" spans="2:7" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3466,18 +3472,18 @@
         <v>14</v>
       </c>
       <c r="C16" s="38">
-        <v>10165</v>
+        <v>23493</v>
       </c>
       <c r="D16" s="38">
-        <v>13651</v>
+        <v>25855</v>
       </c>
       <c r="E16" s="38">
         <f t="shared" si="0"/>
-        <v>3486</v>
+        <v>2362</v>
       </c>
       <c r="F16" s="144">
         <f t="shared" si="1"/>
-        <v>0.34294146581406793</v>
+        <v>0.10054058655769804</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3485,18 +3491,18 @@
         <v>15</v>
       </c>
       <c r="C17" s="38">
-        <v>1473</v>
+        <v>2387</v>
       </c>
       <c r="D17" s="38">
-        <v>1922</v>
+        <v>3155</v>
       </c>
       <c r="E17" s="38">
         <f t="shared" si="0"/>
-        <v>449</v>
+        <v>768</v>
       </c>
       <c r="F17" s="144">
         <f t="shared" si="1"/>
-        <v>0.30482009504412755</v>
+        <v>0.32174277335567658</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3504,18 +3510,18 @@
         <v>16</v>
       </c>
       <c r="C18" s="38">
-        <v>219264</v>
+        <v>361835</v>
       </c>
       <c r="D18" s="38">
-        <v>230717</v>
+        <v>380108</v>
       </c>
       <c r="E18" s="38">
         <f t="shared" si="0"/>
-        <v>11453</v>
+        <v>18273</v>
       </c>
       <c r="F18" s="144">
         <f t="shared" si="1"/>
-        <v>5.2233836835960279E-2</v>
+        <v>5.0500918927135263E-2</v>
       </c>
     </row>
     <row r="19" spans="2:6" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3523,18 +3529,18 @@
         <v>17</v>
       </c>
       <c r="C19" s="38">
-        <v>1240</v>
+        <v>1602</v>
       </c>
       <c r="D19" s="38">
-        <v>2326</v>
+        <v>2422</v>
       </c>
       <c r="E19" s="38">
         <f t="shared" si="0"/>
-        <v>1086</v>
+        <v>820</v>
       </c>
       <c r="F19" s="144">
         <f t="shared" si="1"/>
-        <v>0.87580645161290316</v>
+        <v>0.51186017478152301</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3542,18 +3548,18 @@
         <v>3</v>
       </c>
       <c r="C20" s="38">
-        <v>180805</v>
+        <v>209983</v>
       </c>
       <c r="D20" s="38">
-        <v>160473</v>
+        <v>199577</v>
       </c>
       <c r="E20" s="38">
         <f t="shared" si="0"/>
-        <v>-20332</v>
+        <v>-10406</v>
       </c>
       <c r="F20" s="144">
         <f t="shared" si="1"/>
-        <v>-0.11245264234949259</v>
+        <v>-4.9556392660358273E-2</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3561,18 +3567,18 @@
         <v>18</v>
       </c>
       <c r="C21" s="38">
-        <v>673</v>
+        <v>1132</v>
       </c>
       <c r="D21" s="38">
-        <v>909</v>
+        <v>1382</v>
       </c>
       <c r="E21" s="38">
         <f t="shared" si="0"/>
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="F21" s="144">
         <f t="shared" si="1"/>
-        <v>0.35066864784546814</v>
+        <v>0.22084805653710249</v>
       </c>
     </row>
     <row r="22" spans="2:6" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3580,18 +3586,18 @@
         <v>21</v>
       </c>
       <c r="C22" s="38">
-        <v>10151</v>
+        <v>19225</v>
       </c>
       <c r="D22" s="38">
-        <v>8444</v>
+        <v>19769</v>
       </c>
       <c r="E22" s="38">
         <f t="shared" si="0"/>
-        <v>-1707</v>
+        <v>544</v>
       </c>
       <c r="F22" s="144">
         <f t="shared" si="1"/>
-        <v>-0.16816077233770077</v>
+        <v>2.8296488946683906E-2</v>
       </c>
     </row>
     <row r="23" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3599,18 +3605,18 @@
         <v>20</v>
       </c>
       <c r="C23" s="38">
-        <v>24192</v>
+        <v>32269</v>
       </c>
       <c r="D23" s="38">
-        <v>30119</v>
+        <v>39131</v>
       </c>
       <c r="E23" s="38">
         <f t="shared" si="0"/>
-        <v>5927</v>
+        <v>6862</v>
       </c>
       <c r="F23" s="144">
         <f t="shared" si="1"/>
-        <v>0.24499834656084651</v>
+        <v>0.21264991167994052</v>
       </c>
     </row>
     <row r="24" spans="2:6" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3618,18 +3624,18 @@
         <v>9</v>
       </c>
       <c r="C24" s="38">
-        <v>1204</v>
+        <v>2336</v>
       </c>
       <c r="D24" s="38">
-        <v>1545</v>
+        <v>2950</v>
       </c>
       <c r="E24" s="38">
         <f t="shared" si="0"/>
-        <v>341</v>
+        <v>614</v>
       </c>
       <c r="F24" s="144">
         <f t="shared" si="1"/>
-        <v>0.28322259136212624</v>
+        <v>0.26284246575342474</v>
       </c>
     </row>
     <row r="25" spans="2:6" s="130" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3637,18 +3643,18 @@
         <v>10</v>
       </c>
       <c r="C25" s="129">
-        <v>21625</v>
+        <v>41088</v>
       </c>
       <c r="D25" s="129">
-        <v>21583</v>
+        <v>44943</v>
       </c>
       <c r="E25" s="129">
         <f t="shared" si="0"/>
-        <v>-42</v>
+        <v>3855</v>
       </c>
       <c r="F25" s="145">
         <f t="shared" si="1"/>
-        <v>-1.942196531791951E-3</v>
+        <v>9.3823014018691531E-2</v>
       </c>
     </row>
     <row r="26" spans="2:6" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3656,18 +3662,18 @@
         <v>11</v>
       </c>
       <c r="C26" s="38">
-        <v>3681</v>
+        <v>5752</v>
       </c>
       <c r="D26" s="38">
-        <v>3678</v>
+        <v>5936</v>
       </c>
       <c r="E26" s="38">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>184</v>
       </c>
       <c r="F26" s="144">
         <f t="shared" si="1"/>
-        <v>-8.1499592502032314E-4</v>
+        <v>3.1988873435326859E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3675,18 +3681,18 @@
         <v>7</v>
       </c>
       <c r="C27" s="38">
-        <v>2259</v>
+        <v>3746</v>
       </c>
       <c r="D27" s="38">
-        <v>2868</v>
+        <v>4637</v>
       </c>
       <c r="E27" s="38">
         <f t="shared" si="0"/>
-        <v>609</v>
+        <v>891</v>
       </c>
       <c r="F27" s="144">
         <f t="shared" si="1"/>
-        <v>0.26958831341301459</v>
+        <v>0.23785371062466631</v>
       </c>
     </row>
     <row r="28" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3694,18 +3700,18 @@
         <v>22</v>
       </c>
       <c r="C28" s="52">
-        <v>11473</v>
+        <v>18406</v>
       </c>
       <c r="D28" s="52">
-        <v>15359</v>
+        <v>20921</v>
       </c>
       <c r="E28" s="52">
         <f t="shared" si="0"/>
-        <v>3886</v>
+        <v>2515</v>
       </c>
       <c r="F28" s="143">
         <f t="shared" si="1"/>
-        <v>0.3387082715941776</v>
+        <v>0.13664022601325665</v>
       </c>
     </row>
     <row r="29" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3713,18 +3719,18 @@
         <v>29</v>
       </c>
       <c r="C29" s="38">
-        <v>6506</v>
+        <v>12398</v>
       </c>
       <c r="D29" s="38">
-        <v>9479</v>
+        <v>13320</v>
       </c>
       <c r="E29" s="38">
         <f t="shared" si="0"/>
-        <v>2973</v>
+        <v>922</v>
       </c>
       <c r="F29" s="144">
         <f t="shared" si="1"/>
-        <v>0.45696280356593921</v>
+        <v>7.4366833360219431E-2</v>
       </c>
     </row>
     <row r="30" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3732,18 +3738,18 @@
         <v>23</v>
       </c>
       <c r="C30" s="38">
-        <v>863</v>
+        <v>1077</v>
       </c>
       <c r="D30" s="38">
-        <v>849</v>
+        <v>1253</v>
       </c>
       <c r="E30" s="38">
         <f t="shared" si="0"/>
-        <v>-14</v>
+        <v>176</v>
       </c>
       <c r="F30" s="144">
         <f t="shared" si="1"/>
-        <v>-1.6222479721900385E-2</v>
+        <v>0.16341689879294341</v>
       </c>
     </row>
     <row r="31" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3751,18 +3757,18 @@
         <v>26</v>
       </c>
       <c r="C31" s="38">
-        <v>1015</v>
+        <v>1359</v>
       </c>
       <c r="D31" s="38">
-        <v>1113</v>
+        <v>1434</v>
       </c>
       <c r="E31" s="38">
         <f t="shared" si="0"/>
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="F31" s="144">
         <f t="shared" si="1"/>
-        <v>9.6551724137931005E-2</v>
+        <v>5.5187637969094983E-2</v>
       </c>
     </row>
     <row r="32" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3770,18 +3776,18 @@
         <v>25</v>
       </c>
       <c r="C32" s="38">
-        <v>94</v>
+        <v>140</v>
       </c>
       <c r="D32" s="38">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="E32" s="38">
         <f t="shared" si="0"/>
-        <v>-17</v>
+        <v>-36</v>
       </c>
       <c r="F32" s="144">
         <f t="shared" si="1"/>
-        <v>-0.18085106382978722</v>
+        <v>-0.25714285714285712</v>
       </c>
     </row>
     <row r="33" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3789,18 +3795,18 @@
         <v>27</v>
       </c>
       <c r="C33" s="38">
-        <v>743</v>
+        <v>1145</v>
       </c>
       <c r="D33" s="38">
-        <v>1169</v>
+        <v>1616</v>
       </c>
       <c r="E33" s="38">
         <f t="shared" si="0"/>
-        <v>426</v>
+        <v>471</v>
       </c>
       <c r="F33" s="144">
         <f t="shared" si="1"/>
-        <v>0.57335127860026924</v>
+        <v>0.41135371179039293</v>
       </c>
     </row>
     <row r="34" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3808,18 +3814,18 @@
         <v>24</v>
       </c>
       <c r="C34" s="38">
-        <v>767</v>
+        <v>888</v>
       </c>
       <c r="D34" s="38">
-        <v>974</v>
+        <v>1335</v>
       </c>
       <c r="E34" s="38">
         <f t="shared" si="0"/>
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="F34" s="144">
         <f t="shared" si="1"/>
-        <v>0.26988265971316827</v>
+        <v>0.50337837837837829</v>
       </c>
     </row>
     <row r="35" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3827,18 +3833,18 @@
         <v>28</v>
       </c>
       <c r="C35" s="38">
-        <v>1485</v>
+        <v>1399</v>
       </c>
       <c r="D35" s="38">
-        <v>1698</v>
+        <v>1859</v>
       </c>
       <c r="E35" s="38">
         <f t="shared" si="0"/>
-        <v>213</v>
+        <v>460</v>
       </c>
       <c r="F35" s="144">
         <f t="shared" si="1"/>
-        <v>0.14343434343434347</v>
+        <v>0.32880629020729102</v>
       </c>
     </row>
     <row r="36" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3846,18 +3852,18 @@
         <v>30</v>
       </c>
       <c r="C36" s="52">
-        <v>16008</v>
+        <v>24549</v>
       </c>
       <c r="D36" s="52">
-        <v>22874</v>
+        <v>30663</v>
       </c>
       <c r="E36" s="52">
         <f t="shared" si="0"/>
-        <v>6866</v>
+        <v>6114</v>
       </c>
       <c r="F36" s="143">
         <f t="shared" si="1"/>
-        <v>0.42891054472763623</v>
+        <v>0.24905291457900525</v>
       </c>
     </row>
     <row r="37" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3865,18 +3871,18 @@
         <v>31</v>
       </c>
       <c r="C37" s="38">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="D37" s="38">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="E37" s="38">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F37" s="144">
         <f t="shared" si="1"/>
-        <v>0.16463414634146334</v>
+        <v>0.20540540540540531</v>
       </c>
     </row>
     <row r="38" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3884,18 +3890,18 @@
         <v>32</v>
       </c>
       <c r="C38" s="38">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D38" s="38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E38" s="38">
         <f t="shared" si="0"/>
-        <v>-24</v>
+        <v>-13</v>
       </c>
       <c r="F38" s="144">
         <f t="shared" si="1"/>
-        <v>-0.70588235294117641</v>
+        <v>-0.61904761904761907</v>
       </c>
     </row>
     <row r="39" spans="2:6" ht="12" x14ac:dyDescent="0.2">
@@ -3903,18 +3909,18 @@
         <v>211</v>
       </c>
       <c r="C39" s="38">
-        <v>134</v>
+        <v>199</v>
       </c>
       <c r="D39" s="38">
-        <v>129</v>
+        <v>269</v>
       </c>
       <c r="E39" s="38">
         <f t="shared" si="0"/>
-        <v>-5</v>
+        <v>70</v>
       </c>
       <c r="F39" s="144">
         <f t="shared" si="1"/>
-        <v>-3.7313432835820892E-2</v>
+        <v>0.35175879396984921</v>
       </c>
     </row>
     <row r="40" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3922,18 +3928,18 @@
         <v>42</v>
       </c>
       <c r="C40" s="38">
-        <v>2988</v>
+        <v>4966</v>
       </c>
       <c r="D40" s="38">
-        <v>4315</v>
+        <v>6737</v>
       </c>
       <c r="E40" s="38">
         <f t="shared" si="0"/>
-        <v>1327</v>
+        <v>1771</v>
       </c>
       <c r="F40" s="144">
         <f t="shared" si="1"/>
-        <v>0.44410977242302541</v>
+        <v>0.35662505034232783</v>
       </c>
     </row>
     <row r="41" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3941,18 +3947,18 @@
         <v>35</v>
       </c>
       <c r="C41" s="38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D41" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" s="38">
         <f t="shared" si="0"/>
+        <v>-3</v>
+      </c>
+      <c r="F41" s="144">
+        <f t="shared" si="1"/>
         <v>-1</v>
-      </c>
-      <c r="F41" s="144">
-        <f t="shared" si="1"/>
-        <v>-0.5</v>
       </c>
     </row>
     <row r="42" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3960,37 +3966,37 @@
         <v>36</v>
       </c>
       <c r="C42" s="38">
-        <v>4170</v>
+        <v>6815</v>
       </c>
       <c r="D42" s="38">
-        <v>7117</v>
+        <v>8459</v>
       </c>
       <c r="E42" s="38">
         <f t="shared" si="0"/>
-        <v>2947</v>
+        <v>1644</v>
       </c>
       <c r="F42" s="144">
         <f t="shared" si="1"/>
-        <v>0.7067146282973622</v>
+        <v>0.24123257520176078</v>
       </c>
     </row>
     <row r="43" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B43" s="81" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C43" s="38">
-        <v>210</v>
+        <v>358</v>
       </c>
       <c r="D43" s="38">
-        <v>253</v>
+        <v>334</v>
       </c>
       <c r="E43" s="38">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>-24</v>
       </c>
       <c r="F43" s="144">
         <f t="shared" si="1"/>
-        <v>0.2047619047619047</v>
+        <v>-6.7039106145251437E-2</v>
       </c>
     </row>
     <row r="44" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3998,18 +4004,18 @@
         <v>37</v>
       </c>
       <c r="C44" s="38">
-        <v>94</v>
+        <v>164</v>
       </c>
       <c r="D44" s="38">
-        <v>143</v>
+        <v>233</v>
       </c>
       <c r="E44" s="38">
         <f t="shared" si="0"/>
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="F44" s="144">
         <f t="shared" si="1"/>
-        <v>0.52127659574468077</v>
+        <v>0.4207317073170731</v>
       </c>
     </row>
     <row r="45" spans="2:6" ht="12" x14ac:dyDescent="0.2">
@@ -4017,18 +4023,18 @@
         <v>38</v>
       </c>
       <c r="C45" s="38">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="D45" s="38">
-        <v>93</v>
+        <v>164</v>
       </c>
       <c r="E45" s="38">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F45" s="144">
         <f t="shared" si="1"/>
-        <v>0.2567567567567568</v>
+        <v>0.15492957746478875</v>
       </c>
     </row>
     <row r="46" spans="2:6" ht="12" x14ac:dyDescent="0.2">
@@ -4036,18 +4042,18 @@
         <v>39</v>
       </c>
       <c r="C46" s="38">
-        <v>892</v>
+        <v>1532</v>
       </c>
       <c r="D46" s="38">
-        <v>1114</v>
+        <v>1933</v>
       </c>
       <c r="E46" s="38">
         <f t="shared" si="0"/>
-        <v>222</v>
+        <v>401</v>
       </c>
       <c r="F46" s="144">
         <f t="shared" si="1"/>
-        <v>0.24887892376681608</v>
+        <v>0.26174934725848553</v>
       </c>
     </row>
     <row r="47" spans="2:6" ht="12" x14ac:dyDescent="0.2">
@@ -4055,18 +4061,18 @@
         <v>34</v>
       </c>
       <c r="C47" s="38">
-        <v>5825</v>
+        <v>7837</v>
       </c>
       <c r="D47" s="38">
-        <v>7089</v>
+        <v>7925</v>
       </c>
       <c r="E47" s="38">
         <f t="shared" si="0"/>
-        <v>1264</v>
+        <v>88</v>
       </c>
       <c r="F47" s="144">
         <f t="shared" si="1"/>
-        <v>0.21699570815450642</v>
+        <v>1.1228786525456114E-2</v>
       </c>
     </row>
     <row r="48" spans="2:6" ht="12" x14ac:dyDescent="0.2">
@@ -4074,18 +4080,18 @@
         <v>40</v>
       </c>
       <c r="C48" s="38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D48" s="38">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E48" s="38">
         <f t="shared" si="0"/>
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="F48" s="144">
         <f t="shared" si="1"/>
-        <v>-0.5</v>
+        <v>0.14285714285714279</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4093,18 +4099,18 @@
         <v>212</v>
       </c>
       <c r="C49" s="38">
-        <v>703</v>
+        <v>1135</v>
       </c>
       <c r="D49" s="38">
-        <v>1401</v>
+        <v>2671</v>
       </c>
       <c r="E49" s="38">
         <f t="shared" si="0"/>
-        <v>698</v>
+        <v>1536</v>
       </c>
       <c r="F49" s="144">
         <f t="shared" si="1"/>
-        <v>0.99288762446657186</v>
+        <v>1.3533039647577092</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4112,18 +4118,18 @@
         <v>41</v>
       </c>
       <c r="C50" s="38">
-        <v>415</v>
+        <v>682</v>
       </c>
       <c r="D50" s="38">
-        <v>522</v>
+        <v>962</v>
       </c>
       <c r="E50" s="38">
         <f t="shared" si="0"/>
-        <v>107</v>
+        <v>280</v>
       </c>
       <c r="F50" s="144">
         <f t="shared" si="1"/>
-        <v>0.25783132530120478</v>
+        <v>0.41055718475073322</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4131,18 +4137,18 @@
         <v>33</v>
       </c>
       <c r="C51" s="38">
-        <v>297</v>
+        <v>503</v>
       </c>
       <c r="D51" s="38">
-        <v>493</v>
+        <v>737</v>
       </c>
       <c r="E51" s="38">
         <f t="shared" si="0"/>
-        <v>196</v>
+        <v>234</v>
       </c>
       <c r="F51" s="144">
         <f t="shared" si="1"/>
-        <v>0.65993265993266004</v>
+        <v>0.46520874751491048</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4150,18 +4156,18 @@
         <v>43</v>
       </c>
       <c r="C52" s="52">
-        <v>22143</v>
+        <v>42230</v>
       </c>
       <c r="D52" s="52">
-        <v>28693</v>
+        <v>52721</v>
       </c>
       <c r="E52" s="52">
         <f t="shared" si="0"/>
-        <v>6550</v>
+        <v>10491</v>
       </c>
       <c r="F52" s="143">
         <f t="shared" si="1"/>
-        <v>0.29580454319649552</v>
+        <v>0.2484252900781434</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4170,18 +4176,18 @@
         <v>60</v>
       </c>
       <c r="C53" s="38">
-        <v>1478</v>
+        <v>2230</v>
       </c>
       <c r="D53" s="38">
-        <v>1537</v>
+        <v>2884</v>
       </c>
       <c r="E53" s="38">
         <f t="shared" si="0"/>
-        <v>59</v>
+        <v>654</v>
       </c>
       <c r="F53" s="144">
         <f t="shared" si="1"/>
-        <v>3.9918809201623828E-2</v>
+        <v>0.29327354260089677</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4190,18 +4196,18 @@
         <v>44</v>
       </c>
       <c r="C54" s="38">
-        <v>1371</v>
+        <v>2307</v>
       </c>
       <c r="D54" s="38">
-        <v>1632</v>
+        <v>2687</v>
       </c>
       <c r="E54" s="38">
         <f t="shared" si="0"/>
-        <v>261</v>
+        <v>380</v>
       </c>
       <c r="F54" s="144">
         <f t="shared" si="1"/>
-        <v>0.19037199124726478</v>
+        <v>0.16471608149111394</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4210,18 +4216,18 @@
         <v>46</v>
       </c>
       <c r="C55" s="38">
-        <v>10212</v>
+        <v>22180</v>
       </c>
       <c r="D55" s="38">
-        <v>14051</v>
+        <v>26841</v>
       </c>
       <c r="E55" s="38">
         <f t="shared" si="0"/>
-        <v>3839</v>
+        <v>4661</v>
       </c>
       <c r="F55" s="144">
         <f t="shared" si="1"/>
-        <v>0.37593027810419111</v>
+        <v>0.21014427412082948</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
@@ -4230,18 +4236,18 @@
         <v>47</v>
       </c>
       <c r="C56" s="38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D56" s="38">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E56" s="38">
         <f t="shared" si="0"/>
-        <v>-4</v>
+        <v>13</v>
       </c>
       <c r="F56" s="144">
         <f t="shared" si="1"/>
-        <v>-0.5714285714285714</v>
+        <v>1.625</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
@@ -4250,18 +4256,18 @@
         <v>48</v>
       </c>
       <c r="C57" s="38">
-        <v>75</v>
+        <v>169</v>
       </c>
       <c r="D57" s="38">
-        <v>102</v>
+        <v>199</v>
       </c>
       <c r="E57" s="38">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F57" s="144">
         <f t="shared" si="1"/>
-        <v>0.3600000000000001</v>
+        <v>0.1775147928994083</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
@@ -4273,15 +4279,15 @@
         <v>4</v>
       </c>
       <c r="D58" s="38">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E58" s="38">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F58" s="144">
         <f t="shared" si="1"/>
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.2">
@@ -4290,18 +4296,18 @@
         <v>49</v>
       </c>
       <c r="C59" s="38">
-        <v>2736</v>
+        <v>4885</v>
       </c>
       <c r="D59" s="38">
-        <v>3441</v>
+        <v>6621</v>
       </c>
       <c r="E59" s="38">
         <f t="shared" si="0"/>
-        <v>705</v>
+        <v>1736</v>
       </c>
       <c r="F59" s="144">
         <f t="shared" si="1"/>
-        <v>0.25767543859649122</v>
+        <v>0.3553735926305015</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4310,18 +4316,18 @@
         <v>45</v>
       </c>
       <c r="C60" s="38">
-        <v>5008</v>
+        <v>7877</v>
       </c>
       <c r="D60" s="38">
-        <v>6243</v>
+        <v>10082</v>
       </c>
       <c r="E60" s="38">
         <f t="shared" si="0"/>
-        <v>1235</v>
+        <v>2205</v>
       </c>
       <c r="F60" s="144">
         <f t="shared" si="1"/>
-        <v>0.2466054313099042</v>
+        <v>0.27992890694426809</v>
       </c>
     </row>
     <row r="61" spans="1:6" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4330,18 +4336,18 @@
         <v>50</v>
       </c>
       <c r="C61" s="38">
-        <v>1252</v>
+        <v>2570</v>
       </c>
       <c r="D61" s="38">
-        <v>1674</v>
+        <v>3381</v>
       </c>
       <c r="E61" s="38">
         <f t="shared" si="0"/>
-        <v>422</v>
+        <v>811</v>
       </c>
       <c r="F61" s="144">
         <f t="shared" si="1"/>
-        <v>0.33706070287539935</v>
+        <v>0.31556420233463034</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4349,18 +4355,18 @@
         <v>51</v>
       </c>
       <c r="C62" s="52">
-        <v>307524</v>
+        <v>400283</v>
       </c>
       <c r="D62" s="52">
-        <v>306862</v>
+        <v>368905</v>
       </c>
       <c r="E62" s="52">
         <f t="shared" si="0"/>
-        <v>-662</v>
+        <v>-31378</v>
       </c>
       <c r="F62" s="143">
         <f t="shared" si="1"/>
-        <v>-2.1526775146004651E-3</v>
+        <v>-7.8389539400873898E-2</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4368,18 +4374,18 @@
         <v>54</v>
       </c>
       <c r="C63" s="38">
-        <v>225265</v>
+        <v>308349</v>
       </c>
       <c r="D63" s="38">
-        <v>238368</v>
+        <v>287012</v>
       </c>
       <c r="E63" s="38">
         <f t="shared" si="0"/>
-        <v>13103</v>
+        <v>-21337</v>
       </c>
       <c r="F63" s="144">
         <f t="shared" si="1"/>
-        <v>5.8167047699376306E-2</v>
+        <v>-6.9197565096692393E-2</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4387,18 +4393,18 @@
         <v>53</v>
       </c>
       <c r="C64" s="38">
-        <v>80896</v>
+        <v>90398</v>
       </c>
       <c r="D64" s="38">
-        <v>66744</v>
+        <v>79884</v>
       </c>
       <c r="E64" s="38">
         <f t="shared" si="0"/>
-        <v>-14152</v>
+        <v>-10514</v>
       </c>
       <c r="F64" s="144">
         <f t="shared" si="1"/>
-        <v>-0.174940664556962</v>
+        <v>-0.11630788291776362</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4406,18 +4412,18 @@
         <v>52</v>
       </c>
       <c r="C65" s="38">
-        <v>1363</v>
+        <v>1536</v>
       </c>
       <c r="D65" s="38">
-        <v>1750</v>
+        <v>2009</v>
       </c>
       <c r="E65" s="38">
         <f t="shared" si="0"/>
-        <v>387</v>
+        <v>473</v>
       </c>
       <c r="F65" s="144">
         <f t="shared" si="1"/>
-        <v>0.28393250183418939</v>
+        <v>0.30794270833333326</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4425,18 +4431,18 @@
         <v>55</v>
       </c>
       <c r="C66" s="53">
-        <v>10920</v>
+        <v>20239</v>
       </c>
       <c r="D66" s="53">
-        <v>12909</v>
+        <v>20228</v>
       </c>
       <c r="E66" s="53">
         <f t="shared" si="0"/>
-        <v>1989</v>
+        <v>-11</v>
       </c>
       <c r="F66" s="146">
         <f t="shared" si="1"/>
-        <v>0.18214285714285716</v>
+        <v>-5.4350511388900902E-4</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
@@ -4444,18 +4450,18 @@
         <v>56</v>
       </c>
       <c r="C67" s="54">
-        <v>228</v>
+        <v>330</v>
       </c>
       <c r="D67" s="52">
-        <v>304</v>
+        <v>334</v>
       </c>
       <c r="E67" s="54">
         <f t="shared" si="0"/>
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="F67" s="147">
         <f t="shared" si="1"/>
-        <v>0.33333333333333326</v>
+        <v>1.2121212121212199E-2</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
@@ -4481,18 +4487,18 @@
         <v>57</v>
       </c>
       <c r="C69" s="38">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D69" s="38">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E69" s="38">
         <f t="shared" ref="E69:E83" si="3">D69-C69</f>
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="F69" s="144">
-        <f t="shared" ref="F69:F86" si="4">D69/C69-1</f>
-        <v>0.33333333333333326</v>
+        <f t="shared" ref="F69:F87" si="4">D69/C69-1</f>
+        <v>-0.3529411764705882</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
@@ -4504,15 +4510,15 @@
         <v>1</v>
       </c>
       <c r="D70" s="38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E70" s="38">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F70" s="144">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
@@ -4521,18 +4527,18 @@
         <v>58</v>
       </c>
       <c r="C71" s="38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D71" s="38">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E71" s="38">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71" s="144">
         <f t="shared" si="4"/>
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
@@ -4541,18 +4547,18 @@
         <v>185</v>
       </c>
       <c r="C72" s="38">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D72" s="38">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E72" s="38">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F72" s="144">
         <f t="shared" si="4"/>
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4561,18 +4567,18 @@
         <v>74</v>
       </c>
       <c r="C73" s="38">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="D73" s="38">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E73" s="38">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>-14</v>
       </c>
       <c r="F73" s="144">
         <f t="shared" si="4"/>
-        <v>0.19753086419753085</v>
+        <v>-0.12962962962962965</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4581,18 +4587,18 @@
         <v>75</v>
       </c>
       <c r="C74" s="38">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D74" s="38">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E74" s="38">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F74" s="144">
         <f t="shared" si="4"/>
-        <v>1.9166666666666665</v>
+        <v>0.28125</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
@@ -4635,18 +4641,18 @@
         <v>86</v>
       </c>
       <c r="C77" s="38">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D77" s="38">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E77" s="38">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F77" s="144">
         <f t="shared" si="4"/>
-        <v>0.33333333333333326</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4672,18 +4678,18 @@
         <v>102</v>
       </c>
       <c r="C79" s="38">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D79" s="38">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E79" s="38">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F79" s="144">
         <f t="shared" si="4"/>
-        <v>2.4390243902439046E-2</v>
+        <v>-2.6315789473684181E-2</v>
       </c>
     </row>
     <row r="80" spans="1:6" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -4726,16 +4732,19 @@
         <v>130</v>
       </c>
       <c r="C82" s="38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D82" s="38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82" s="38">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="F82" s="144"/>
+        <v>0</v>
+      </c>
+      <c r="F82" s="144">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="83" spans="1:6" s="20" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="11"/>
@@ -4743,18 +4752,18 @@
         <v>131</v>
       </c>
       <c r="C83" s="38">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="D83" s="38">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E83" s="38">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>-24</v>
       </c>
       <c r="F83" s="144">
         <f t="shared" si="4"/>
-        <v>0.58974358974358965</v>
+        <v>-0.27272727272727271</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4763,18 +4772,18 @@
         <v>190</v>
       </c>
       <c r="C84" s="38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D84" s="38">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E84" s="38">
         <f t="shared" ref="E84:E134" si="5">D84-C84</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F84" s="144">
         <f t="shared" si="4"/>
-        <v>0.33333333333333326</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4800,18 +4809,18 @@
         <v>141</v>
       </c>
       <c r="C86" s="38">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D86" s="38">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E86" s="38">
         <f t="shared" si="5"/>
-        <v>-7</v>
+        <v>5</v>
       </c>
       <c r="F86" s="144">
         <f t="shared" si="4"/>
-        <v>-0.77777777777777779</v>
+        <v>0.83333333333333326</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4820,18 +4829,18 @@
         <v>151</v>
       </c>
       <c r="C87" s="38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87" s="38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E87" s="38">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F87" s="144">
-        <f t="shared" ref="F87" si="6">D87/C87-1</f>
-        <v>0.5</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4839,18 +4848,18 @@
         <v>195</v>
       </c>
       <c r="C88" s="52">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="D88" s="52">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="E88" s="52">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>-25</v>
       </c>
       <c r="F88" s="143">
-        <f t="shared" ref="F88:F138" si="7">D88/C88-1</f>
-        <v>7.2164948453608213E-2</v>
+        <f t="shared" ref="F88:F138" si="6">D88/C88-1</f>
+        <v>-0.17123287671232879</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4858,34 +4867,37 @@
         <v>186</v>
       </c>
       <c r="C89" s="38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D89" s="38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E89" s="38">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="F89" s="144"/>
+        <v>-2</v>
+      </c>
+      <c r="F89" s="144">
+        <f>D89/C89-1</f>
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="90" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B90" s="85" t="s">
         <v>155</v>
       </c>
       <c r="C90" s="38">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D90" s="38">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E90" s="38">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F90" s="144">
-        <f t="shared" si="7"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="6"/>
+        <v>0.21428571428571419</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="12" x14ac:dyDescent="0.2">
@@ -4893,18 +4905,18 @@
         <v>100</v>
       </c>
       <c r="C91" s="38">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="D91" s="38">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="E91" s="38">
         <f t="shared" si="5"/>
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="F91" s="144">
-        <f t="shared" si="7"/>
-        <v>-4.8780487804878092E-2</v>
+        <f t="shared" si="6"/>
+        <v>-0.14516129032258063</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4912,17 +4924,17 @@
         <v>164</v>
       </c>
       <c r="C92" s="38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D92" s="38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F92" s="144">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -4931,18 +4943,18 @@
         <v>119</v>
       </c>
       <c r="C93" s="38">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D93" s="38">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E93" s="38">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>-11</v>
       </c>
       <c r="F93" s="144">
-        <f t="shared" si="7"/>
-        <v>4.5454545454545414E-2</v>
+        <f t="shared" si="6"/>
+        <v>-0.43999999999999995</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4950,18 +4962,18 @@
         <v>124</v>
       </c>
       <c r="C94" s="38">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D94" s="38">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E94" s="38">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>-11</v>
       </c>
       <c r="F94" s="144">
-        <f t="shared" si="7"/>
-        <v>0.46153846153846145</v>
+        <f t="shared" si="6"/>
+        <v>-0.43999999999999995</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4969,18 +4981,18 @@
         <v>152</v>
       </c>
       <c r="C95" s="38">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D95" s="38">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E95" s="38">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F95" s="144">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>0.33333333333333326</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4989,18 +5001,18 @@
         <v>196</v>
       </c>
       <c r="C96" s="52">
-        <v>9136</v>
+        <v>17595</v>
       </c>
       <c r="D96" s="52">
-        <v>10818</v>
+        <v>17384</v>
       </c>
       <c r="E96" s="52">
         <f t="shared" si="5"/>
-        <v>1682</v>
+        <v>-211</v>
       </c>
       <c r="F96" s="143">
-        <f t="shared" si="7"/>
-        <v>0.18410683012259188</v>
+        <f t="shared" si="6"/>
+        <v>-1.1992043194089197E-2</v>
       </c>
     </row>
     <row r="97" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5008,18 +5020,18 @@
         <v>64</v>
       </c>
       <c r="C97" s="38">
-        <v>7558</v>
+        <v>14666</v>
       </c>
       <c r="D97" s="38">
-        <v>9015</v>
+        <v>14176</v>
       </c>
       <c r="E97" s="38">
         <f t="shared" si="5"/>
-        <v>1457</v>
+        <v>-490</v>
       </c>
       <c r="F97" s="144">
-        <f t="shared" si="7"/>
-        <v>0.19277586663138391</v>
+        <f t="shared" si="6"/>
+        <v>-3.3410609573162442E-2</v>
       </c>
     </row>
     <row r="98" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5027,18 +5039,18 @@
         <v>95</v>
       </c>
       <c r="C98" s="38">
-        <v>1355</v>
+        <v>2532</v>
       </c>
       <c r="D98" s="38">
-        <v>1478</v>
+        <v>2655</v>
       </c>
       <c r="E98" s="38">
         <f t="shared" si="5"/>
         <v>123</v>
       </c>
       <c r="F98" s="144">
-        <f t="shared" si="7"/>
-        <v>9.0774907749077594E-2</v>
+        <f t="shared" si="6"/>
+        <v>4.8578199052132787E-2</v>
       </c>
     </row>
     <row r="99" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5046,18 +5058,18 @@
         <v>110</v>
       </c>
       <c r="C99" s="38">
-        <v>223</v>
+        <v>397</v>
       </c>
       <c r="D99" s="38">
-        <v>325</v>
+        <v>553</v>
       </c>
       <c r="E99" s="38">
         <f t="shared" si="5"/>
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="F99" s="144">
-        <f t="shared" si="7"/>
-        <v>0.45739910313901344</v>
+        <f t="shared" si="6"/>
+        <v>0.39294710327455928</v>
       </c>
     </row>
     <row r="100" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5065,18 +5077,18 @@
         <v>197</v>
       </c>
       <c r="C100" s="52">
-        <v>1459</v>
+        <v>2168</v>
       </c>
       <c r="D100" s="52">
-        <v>1683</v>
+        <v>2389</v>
       </c>
       <c r="E100" s="52">
         <f t="shared" si="5"/>
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F100" s="143">
-        <f t="shared" si="7"/>
-        <v>0.15352981494174101</v>
+        <f t="shared" si="6"/>
+        <v>0.10193726937269365</v>
       </c>
     </row>
     <row r="101" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5084,18 +5096,18 @@
         <v>66</v>
       </c>
       <c r="C101" s="38">
-        <v>205</v>
+        <v>349</v>
       </c>
       <c r="D101" s="38">
-        <v>246</v>
+        <v>366</v>
       </c>
       <c r="E101" s="38">
         <f t="shared" si="5"/>
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F101" s="144">
-        <f t="shared" si="7"/>
-        <v>0.19999999999999996</v>
+        <f t="shared" si="6"/>
+        <v>4.871060171919761E-2</v>
       </c>
     </row>
     <row r="102" spans="2:6" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5103,18 +5115,18 @@
         <v>70</v>
       </c>
       <c r="C102" s="38">
+        <v>21</v>
+      </c>
+      <c r="D102" s="38">
         <v>18</v>
-      </c>
-      <c r="D102" s="38">
-        <v>15</v>
       </c>
       <c r="E102" s="38">
         <f t="shared" si="5"/>
         <v>-3</v>
       </c>
       <c r="F102" s="144">
-        <f t="shared" si="7"/>
-        <v>-0.16666666666666663</v>
+        <f t="shared" si="6"/>
+        <v>-0.1428571428571429</v>
       </c>
     </row>
     <row r="103" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5122,18 +5134,18 @@
         <v>71</v>
       </c>
       <c r="C103" s="38">
-        <v>684</v>
+        <v>1068</v>
       </c>
       <c r="D103" s="38">
-        <v>793</v>
+        <v>1269</v>
       </c>
       <c r="E103" s="38">
         <f t="shared" si="5"/>
-        <v>109</v>
+        <v>201</v>
       </c>
       <c r="F103" s="144">
-        <f t="shared" si="7"/>
-        <v>0.15935672514619892</v>
+        <f t="shared" si="6"/>
+        <v>0.1882022471910112</v>
       </c>
     </row>
     <row r="104" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5144,15 +5156,15 @@
         <v>1</v>
       </c>
       <c r="D104" s="38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E104" s="38">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F104" s="144">
-        <f t="shared" si="7"/>
-        <v>1</v>
+        <f t="shared" si="6"/>
+        <v>2</v>
       </c>
     </row>
     <row r="105" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5160,18 +5172,18 @@
         <v>78</v>
       </c>
       <c r="C105" s="38">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="D105" s="38">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E105" s="38">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>-5</v>
       </c>
       <c r="F105" s="144">
-        <f t="shared" si="7"/>
-        <v>0.234375</v>
+        <f t="shared" si="6"/>
+        <v>-6.4102564102564097E-2</v>
       </c>
     </row>
     <row r="106" spans="2:6" ht="12" x14ac:dyDescent="0.2">
@@ -5179,37 +5191,37 @@
         <v>81</v>
       </c>
       <c r="C106" s="38">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D106" s="38">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E106" s="38">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F106" s="144">
-        <f t="shared" si="7"/>
-        <v>0.21212121212121215</v>
+        <f t="shared" si="6"/>
+        <v>0.12000000000000011</v>
       </c>
     </row>
     <row r="107" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B107" s="82" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C107" s="38">
-        <v>289</v>
+        <v>365</v>
       </c>
       <c r="D107" s="38">
-        <v>250</v>
+        <v>332</v>
       </c>
       <c r="E107" s="38">
         <f t="shared" si="5"/>
-        <v>-39</v>
+        <v>-33</v>
       </c>
       <c r="F107" s="144">
-        <f t="shared" si="7"/>
-        <v>-0.13494809688581311</v>
+        <f t="shared" si="6"/>
+        <v>-9.0410958904109551E-2</v>
       </c>
     </row>
     <row r="108" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5217,18 +5229,18 @@
         <v>121</v>
       </c>
       <c r="C108" s="38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D108" s="38">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E108" s="38">
         <f t="shared" si="5"/>
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F108" s="144">
-        <f t="shared" si="7"/>
-        <v>-9.9999999999999978E-2</v>
+        <f t="shared" si="6"/>
+        <v>1.1111111111111112</v>
       </c>
     </row>
     <row r="109" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5236,18 +5248,18 @@
         <v>122</v>
       </c>
       <c r="C109" s="38">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="D109" s="38">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="E109" s="38">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F109" s="144">
-        <f t="shared" si="7"/>
-        <v>0.24590163934426235</v>
+        <f t="shared" si="6"/>
+        <v>9.7826086956521729E-2</v>
       </c>
     </row>
     <row r="110" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5274,11 +5286,11 @@
         <v>0</v>
       </c>
       <c r="D111" s="38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E111" s="38">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="144"/>
     </row>
@@ -5287,18 +5299,18 @@
         <v>145</v>
       </c>
       <c r="C112" s="38">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D112" s="38">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="E112" s="38">
         <f t="shared" si="5"/>
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="F112" s="144">
-        <f t="shared" si="7"/>
-        <v>3.9375</v>
+        <f t="shared" si="6"/>
+        <v>0.10526315789473695</v>
       </c>
     </row>
     <row r="113" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5306,18 +5318,18 @@
         <v>149</v>
       </c>
       <c r="C113" s="38">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="D113" s="38">
-        <v>93</v>
+        <v>136</v>
       </c>
       <c r="E113" s="38">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F113" s="144">
-        <f t="shared" si="7"/>
-        <v>0.19230769230769229</v>
+        <f t="shared" si="6"/>
+        <v>0.11475409836065564</v>
       </c>
     </row>
     <row r="114" spans="2:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5325,18 +5337,18 @@
         <v>198</v>
       </c>
       <c r="C114" s="53">
-        <v>90672</v>
+        <v>151759</v>
       </c>
       <c r="D114" s="53">
-        <v>70833</v>
+        <v>88125</v>
       </c>
       <c r="E114" s="53">
         <f t="shared" si="5"/>
-        <v>-19839</v>
+        <v>-63634</v>
       </c>
       <c r="F114" s="146">
-        <f t="shared" si="7"/>
-        <v>-0.21879962943356268</v>
+        <f t="shared" si="6"/>
+        <v>-0.41930956318900359</v>
       </c>
     </row>
     <row r="115" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5344,18 +5356,18 @@
         <v>199</v>
       </c>
       <c r="C115" s="52">
-        <v>16437</v>
+        <v>50331</v>
       </c>
       <c r="D115" s="52">
-        <v>23660</v>
+        <v>47898</v>
       </c>
       <c r="E115" s="52">
         <f t="shared" si="5"/>
-        <v>7223</v>
+        <v>-2433</v>
       </c>
       <c r="F115" s="143">
-        <f t="shared" si="7"/>
-        <v>0.43943542008882397</v>
+        <f t="shared" si="6"/>
+        <v>-4.8339989271025785E-2</v>
       </c>
     </row>
     <row r="116" spans="2:6" ht="12" x14ac:dyDescent="0.2">
@@ -5363,18 +5375,18 @@
         <v>87</v>
       </c>
       <c r="C116" s="38">
-        <v>1471</v>
+        <v>2501</v>
       </c>
       <c r="D116" s="38">
-        <v>1344</v>
+        <v>2180</v>
       </c>
       <c r="E116" s="38">
         <f t="shared" si="5"/>
-        <v>-127</v>
+        <v>-321</v>
       </c>
       <c r="F116" s="144">
-        <f t="shared" si="7"/>
-        <v>-8.6335825968728797E-2</v>
+        <f t="shared" si="6"/>
+        <v>-0.12834866053578564</v>
       </c>
     </row>
     <row r="117" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5382,18 +5394,18 @@
         <v>99</v>
       </c>
       <c r="C117" s="38">
-        <v>936</v>
+        <v>14806</v>
       </c>
       <c r="D117" s="38">
-        <v>1565</v>
+        <v>11570</v>
       </c>
       <c r="E117" s="38">
         <f t="shared" si="5"/>
-        <v>629</v>
+        <v>-3236</v>
       </c>
       <c r="F117" s="144">
-        <f t="shared" si="7"/>
-        <v>0.67200854700854706</v>
+        <f t="shared" si="6"/>
+        <v>-0.21856004322571931</v>
       </c>
     </row>
     <row r="118" spans="2:6" ht="12" x14ac:dyDescent="0.2">
@@ -5401,18 +5413,18 @@
         <v>113</v>
       </c>
       <c r="C118" s="38">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="D118" s="38">
-        <v>136</v>
+        <v>206</v>
       </c>
       <c r="E118" s="38">
         <f t="shared" si="5"/>
-        <v>-19</v>
+        <v>67</v>
       </c>
       <c r="F118" s="144">
-        <f t="shared" si="7"/>
-        <v>-0.1225806451612903</v>
+        <f t="shared" si="6"/>
+        <v>0.48201438848920852</v>
       </c>
     </row>
     <row r="119" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5420,34 +5432,37 @@
         <v>138</v>
       </c>
       <c r="C119" s="38">
+        <v>1</v>
+      </c>
+      <c r="D119" s="38">
         <v>0</v>
-      </c>
-      <c r="D119" s="38">
-        <v>1</v>
       </c>
       <c r="E119" s="38">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="F119" s="144"/>
+        <v>-1</v>
+      </c>
+      <c r="F119" s="144">
+        <f t="shared" si="6"/>
+        <v>-1</v>
+      </c>
     </row>
     <row r="120" spans="2:6" ht="12" x14ac:dyDescent="0.2">
       <c r="B120" s="83" t="s">
         <v>150</v>
       </c>
       <c r="C120" s="38">
-        <v>13875</v>
+        <v>32880</v>
       </c>
       <c r="D120" s="38">
-        <v>20612</v>
+        <v>33942</v>
       </c>
       <c r="E120" s="38">
         <f t="shared" si="5"/>
-        <v>6737</v>
+        <v>1062</v>
       </c>
       <c r="F120" s="144">
-        <f t="shared" si="7"/>
-        <v>0.48554954954954965</v>
+        <f t="shared" si="6"/>
+        <v>3.2299270072992714E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5471,34 +5486,37 @@
         <v>160</v>
       </c>
       <c r="C122" s="38">
+        <v>4</v>
+      </c>
+      <c r="D122" s="38">
         <v>0</v>
-      </c>
-      <c r="D122" s="38">
-        <v>2</v>
       </c>
       <c r="E122" s="38">
         <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="F122" s="144"/>
+        <v>-4</v>
+      </c>
+      <c r="F122" s="144">
+        <f t="shared" si="6"/>
+        <v>-1</v>
+      </c>
     </row>
     <row r="123" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B123" s="80" t="s">
         <v>200</v>
       </c>
       <c r="C123" s="52">
-        <v>1310</v>
+        <v>3156</v>
       </c>
       <c r="D123" s="52">
-        <v>1549</v>
+        <v>2719</v>
       </c>
       <c r="E123" s="52">
         <f t="shared" si="5"/>
-        <v>239</v>
+        <v>-437</v>
       </c>
       <c r="F123" s="143">
-        <f t="shared" si="7"/>
-        <v>0.1824427480916031</v>
+        <f t="shared" si="6"/>
+        <v>-0.13846641318124209</v>
       </c>
     </row>
     <row r="124" spans="2:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5506,18 +5524,18 @@
         <v>59</v>
       </c>
       <c r="C124" s="38">
-        <v>1122</v>
+        <v>2656</v>
       </c>
       <c r="D124" s="38">
-        <v>1278</v>
+        <v>2241</v>
       </c>
       <c r="E124" s="38">
         <f t="shared" si="5"/>
-        <v>156</v>
+        <v>-415</v>
       </c>
       <c r="F124" s="144">
-        <f t="shared" si="7"/>
-        <v>0.1390374331550801</v>
+        <f t="shared" si="6"/>
+        <v>-0.15625</v>
       </c>
     </row>
     <row r="125" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5541,18 +5559,18 @@
         <v>67</v>
       </c>
       <c r="C126" s="38">
-        <v>162</v>
+        <v>456</v>
       </c>
       <c r="D126" s="38">
-        <v>245</v>
+        <v>446</v>
       </c>
       <c r="E126" s="38">
         <f t="shared" si="5"/>
-        <v>83</v>
+        <v>-10</v>
       </c>
       <c r="F126" s="144">
-        <f t="shared" si="7"/>
-        <v>0.51234567901234573</v>
+        <f t="shared" si="6"/>
+        <v>-2.1929824561403466E-2</v>
       </c>
     </row>
     <row r="127" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5560,18 +5578,18 @@
         <v>162</v>
       </c>
       <c r="C127" s="38">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D127" s="38">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E127" s="38">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="F127" s="144">
-        <f t="shared" si="7"/>
-        <v>0.26666666666666661</v>
+        <f t="shared" si="6"/>
+        <v>-7.407407407407407E-2</v>
       </c>
     </row>
     <row r="128" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5697,7 +5715,7 @@
         <v>0</v>
       </c>
       <c r="E135" s="38">
-        <f t="shared" ref="E135:E137" si="8">D135-C135</f>
+        <f t="shared" ref="E135:E137" si="7">D135-C135</f>
         <v>0</v>
       </c>
       <c r="F135" s="144"/>
@@ -5707,16 +5725,19 @@
         <v>178</v>
       </c>
       <c r="C136" s="38">
+        <v>1</v>
+      </c>
+      <c r="D136" s="38">
+        <v>1</v>
+      </c>
+      <c r="E136" s="38">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="D136" s="38">
-        <v>2</v>
-      </c>
-      <c r="E136" s="38">
-        <f t="shared" si="8"/>
-        <v>2</v>
-      </c>
-      <c r="F136" s="144"/>
+      <c r="F136" s="144">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="137" spans="1:6" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B137" s="83" t="s">
@@ -5729,7 +5750,7 @@
         <v>0</v>
       </c>
       <c r="E137" s="38">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F137" s="144"/>
@@ -5739,18 +5760,18 @@
         <v>179</v>
       </c>
       <c r="C138" s="38">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D138" s="38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E138" s="38">
-        <f t="shared" ref="E138:E197" si="9">D138-C138</f>
-        <v>-6</v>
+        <f t="shared" ref="E138:E197" si="8">D138-C138</f>
+        <v>-10</v>
       </c>
       <c r="F138" s="144">
-        <f t="shared" si="7"/>
-        <v>-0.54545454545454541</v>
+        <f t="shared" si="6"/>
+        <v>-0.625</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5758,18 +5779,18 @@
         <v>201</v>
       </c>
       <c r="C139" s="52">
-        <v>57735</v>
+        <v>84197</v>
       </c>
       <c r="D139" s="52">
-        <v>34404</v>
+        <v>29375</v>
       </c>
       <c r="E139" s="52">
-        <f t="shared" si="9"/>
-        <v>-23331</v>
+        <f t="shared" si="8"/>
+        <v>-54822</v>
       </c>
       <c r="F139" s="143">
-        <f t="shared" ref="F139:F197" si="10">D139/C139-1</f>
-        <v>-0.4041049623278774</v>
+        <f t="shared" ref="F139:F197" si="9">D139/C139-1</f>
+        <v>-0.65111583548107421</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5778,18 +5799,18 @@
         <v>61</v>
       </c>
       <c r="C140" s="38">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D140" s="38">
-        <v>62</v>
+        <v>151</v>
       </c>
       <c r="E140" s="38">
+        <f t="shared" si="8"/>
+        <v>44</v>
+      </c>
+      <c r="F140" s="144">
         <f t="shared" si="9"/>
-        <v>-35</v>
-      </c>
-      <c r="F140" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.36082474226804129</v>
+        <v>0.41121495327102808</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5798,18 +5819,18 @@
         <v>68</v>
       </c>
       <c r="C141" s="38">
-        <v>424</v>
+        <v>344</v>
       </c>
       <c r="D141" s="38">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E141" s="38">
+        <f t="shared" si="8"/>
+        <v>-172</v>
+      </c>
+      <c r="F141" s="144">
         <f t="shared" si="9"/>
-        <v>-255</v>
-      </c>
-      <c r="F141" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.60141509433962259</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="142" spans="1:6" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5818,18 +5839,18 @@
         <v>187</v>
       </c>
       <c r="C142" s="38">
+        <v>34</v>
+      </c>
+      <c r="D142" s="38">
         <v>10</v>
       </c>
-      <c r="D142" s="38">
-        <v>11</v>
-      </c>
       <c r="E142" s="38">
+        <f t="shared" si="8"/>
+        <v>-24</v>
+      </c>
+      <c r="F142" s="144">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="F142" s="144">
-        <f t="shared" si="10"/>
-        <v>0.10000000000000009</v>
+        <v>-0.70588235294117641</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5838,18 +5859,18 @@
         <v>89</v>
       </c>
       <c r="C143" s="38">
-        <v>26372</v>
+        <v>49521</v>
       </c>
       <c r="D143" s="38">
-        <v>18587</v>
+        <v>11967</v>
       </c>
       <c r="E143" s="38">
+        <f t="shared" si="8"/>
+        <v>-37554</v>
+      </c>
+      <c r="F143" s="144">
         <f t="shared" si="9"/>
-        <v>-7785</v>
-      </c>
-      <c r="F143" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.29519945396632796</v>
+        <v>-0.75834494456897072</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
@@ -5858,18 +5879,18 @@
         <v>92</v>
       </c>
       <c r="C144" s="38">
-        <v>26859</v>
+        <v>30433</v>
       </c>
       <c r="D144" s="38">
-        <v>13757</v>
+        <v>15640</v>
       </c>
       <c r="E144" s="38">
+        <f t="shared" si="8"/>
+        <v>-14793</v>
+      </c>
+      <c r="F144" s="144">
         <f t="shared" si="9"/>
-        <v>-13102</v>
-      </c>
-      <c r="F144" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.48780669421795297</v>
+        <v>-0.48608418493083161</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
@@ -5878,18 +5899,18 @@
         <v>173</v>
       </c>
       <c r="C145" s="38">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="D145" s="38">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E145" s="38">
+        <f t="shared" si="8"/>
+        <v>-27</v>
+      </c>
+      <c r="F145" s="144">
         <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="F145" s="144">
-        <f t="shared" si="10"/>
-        <v>4.1666666666666741E-2</v>
+        <v>-0.58695652173913038</v>
       </c>
     </row>
     <row r="146" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5898,18 +5919,18 @@
         <v>114</v>
       </c>
       <c r="C146" s="38">
-        <v>470</v>
+        <v>376</v>
       </c>
       <c r="D146" s="38">
-        <v>253</v>
+        <v>203</v>
       </c>
       <c r="E146" s="38">
+        <f t="shared" si="8"/>
+        <v>-173</v>
+      </c>
+      <c r="F146" s="144">
         <f t="shared" si="9"/>
-        <v>-217</v>
-      </c>
-      <c r="F146" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.46170212765957441</v>
+        <v>-0.46010638297872342</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5918,18 +5939,18 @@
         <v>118</v>
       </c>
       <c r="C147" s="38">
-        <v>2668</v>
+        <v>2739</v>
       </c>
       <c r="D147" s="38">
-        <v>820</v>
+        <v>942</v>
       </c>
       <c r="E147" s="38">
+        <f t="shared" si="8"/>
+        <v>-1797</v>
+      </c>
+      <c r="F147" s="144">
         <f t="shared" si="9"/>
-        <v>-1848</v>
-      </c>
-      <c r="F147" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.6926536731634183</v>
+        <v>-0.65607886089813805</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5938,18 +5959,18 @@
         <v>148</v>
       </c>
       <c r="C148" s="38">
-        <v>811</v>
+        <v>597</v>
       </c>
       <c r="D148" s="38">
-        <v>720</v>
+        <v>271</v>
       </c>
       <c r="E148" s="38">
+        <f t="shared" si="8"/>
+        <v>-326</v>
+      </c>
+      <c r="F148" s="144">
         <f t="shared" si="9"/>
-        <v>-91</v>
-      </c>
-      <c r="F148" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.11220715166461159</v>
+        <v>-0.54606365159128978</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5958,18 +5979,18 @@
         <v>202</v>
       </c>
       <c r="C149" s="52">
-        <v>15190</v>
+        <v>14075</v>
       </c>
       <c r="D149" s="52">
-        <v>11220</v>
+        <v>8133</v>
       </c>
       <c r="E149" s="52">
+        <f t="shared" si="8"/>
+        <v>-5942</v>
+      </c>
+      <c r="F149" s="143">
         <f t="shared" si="9"/>
-        <v>-3970</v>
-      </c>
-      <c r="F149" s="143">
-        <f t="shared" si="10"/>
-        <v>-0.26135615536537193</v>
+        <v>-0.42216696269982235</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5980,15 +6001,15 @@
         <v>4</v>
       </c>
       <c r="D150" s="38">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E150" s="38">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="F150" s="144">
         <f t="shared" si="9"/>
-        <v>-2</v>
-      </c>
-      <c r="F150" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="12" x14ac:dyDescent="0.2">
@@ -5996,18 +6017,18 @@
         <v>82</v>
       </c>
       <c r="C151" s="38">
-        <v>164</v>
+        <v>318</v>
       </c>
       <c r="D151" s="38">
-        <v>302</v>
+        <v>377</v>
       </c>
       <c r="E151" s="38">
+        <f t="shared" si="8"/>
+        <v>59</v>
+      </c>
+      <c r="F151" s="144">
         <f t="shared" si="9"/>
-        <v>138</v>
-      </c>
-      <c r="F151" s="144">
-        <f t="shared" si="10"/>
-        <v>0.84146341463414642</v>
+        <v>0.18553459119496862</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6015,18 +6036,18 @@
         <v>90</v>
       </c>
       <c r="C152" s="38">
-        <v>689</v>
+        <v>909</v>
       </c>
       <c r="D152" s="38">
-        <v>1014</v>
+        <v>913</v>
       </c>
       <c r="E152" s="38">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="F152" s="144">
         <f t="shared" si="9"/>
-        <v>325</v>
-      </c>
-      <c r="F152" s="144">
-        <f t="shared" si="10"/>
-        <v>0.47169811320754707</v>
+        <v>4.4004400440043057E-3</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="12" x14ac:dyDescent="0.2">
@@ -6034,18 +6055,18 @@
         <v>171</v>
       </c>
       <c r="C153" s="38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D153" s="38">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E153" s="38">
+        <f t="shared" si="8"/>
+        <v>37</v>
+      </c>
+      <c r="F153" s="144">
         <f t="shared" si="9"/>
-        <v>20</v>
-      </c>
-      <c r="F153" s="144">
-        <f t="shared" si="10"/>
-        <v>5</v>
+        <v>12.333333333333334</v>
       </c>
     </row>
     <row r="154" spans="1:6" ht="12" x14ac:dyDescent="0.2">
@@ -6053,18 +6074,18 @@
         <v>229</v>
       </c>
       <c r="C154" s="38">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D154" s="38">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E154" s="38">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+      <c r="F154" s="144">
         <f t="shared" si="9"/>
-        <v>4</v>
-      </c>
-      <c r="F154" s="144">
-        <f t="shared" si="10"/>
-        <v>4</v>
+        <v>1.1666666666666665</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6072,18 +6093,18 @@
         <v>107</v>
       </c>
       <c r="C155" s="38">
-        <v>693</v>
+        <v>1365</v>
       </c>
       <c r="D155" s="38">
-        <v>824</v>
+        <v>1099</v>
       </c>
       <c r="E155" s="38">
+        <f t="shared" si="8"/>
+        <v>-266</v>
+      </c>
+      <c r="F155" s="144">
         <f t="shared" si="9"/>
-        <v>131</v>
-      </c>
-      <c r="F155" s="144">
-        <f t="shared" si="10"/>
-        <v>0.18903318903318911</v>
+        <v>-0.19487179487179485</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6091,18 +6112,18 @@
         <v>111</v>
       </c>
       <c r="C156" s="38">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D156" s="38">
-        <v>148</v>
+        <v>31</v>
       </c>
       <c r="E156" s="38">
+        <f t="shared" si="8"/>
+        <v>-95</v>
+      </c>
+      <c r="F156" s="144">
         <f t="shared" si="9"/>
-        <v>15</v>
-      </c>
-      <c r="F156" s="144">
-        <f t="shared" si="10"/>
-        <v>0.11278195488721798</v>
+        <v>-0.75396825396825395</v>
       </c>
     </row>
     <row r="157" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6110,18 +6131,18 @@
         <v>133</v>
       </c>
       <c r="C157" s="38">
-        <v>235</v>
+        <v>950</v>
       </c>
       <c r="D157" s="38">
-        <v>316</v>
+        <v>523</v>
       </c>
       <c r="E157" s="38">
+        <f t="shared" si="8"/>
+        <v>-427</v>
+      </c>
+      <c r="F157" s="144">
         <f t="shared" si="9"/>
-        <v>81</v>
-      </c>
-      <c r="F157" s="144">
-        <f t="shared" si="10"/>
-        <v>0.34468085106382973</v>
+        <v>-0.44947368421052636</v>
       </c>
     </row>
     <row r="158" spans="1:6" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6129,18 +6150,18 @@
         <v>139</v>
       </c>
       <c r="C158" s="38">
-        <v>2967</v>
+        <v>5513</v>
       </c>
       <c r="D158" s="38">
-        <v>1936</v>
+        <v>2202</v>
       </c>
       <c r="E158" s="38">
+        <f t="shared" si="8"/>
+        <v>-3311</v>
+      </c>
+      <c r="F158" s="144">
         <f t="shared" si="9"/>
-        <v>-1031</v>
-      </c>
-      <c r="F158" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.34748904617458709</v>
+        <v>-0.60058044621803008</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6148,18 +6169,18 @@
         <v>146</v>
       </c>
       <c r="C159" s="38">
-        <v>10300</v>
+        <v>4881</v>
       </c>
       <c r="D159" s="38">
-        <v>6649</v>
+        <v>2921</v>
       </c>
       <c r="E159" s="38">
+        <f t="shared" si="8"/>
+        <v>-1960</v>
+      </c>
+      <c r="F159" s="144">
         <f t="shared" si="9"/>
-        <v>-3651</v>
-      </c>
-      <c r="F159" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.35446601941747569</v>
+        <v>-0.40155705797992214</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6167,322 +6188,327 @@
         <v>213</v>
       </c>
       <c r="C160" s="55">
-        <v>26785</v>
+        <v>52891</v>
       </c>
       <c r="D160" s="55">
-        <v>27779</v>
+        <v>22395</v>
       </c>
       <c r="E160" s="55">
+        <f t="shared" si="8"/>
+        <v>-30496</v>
+      </c>
+      <c r="F160" s="148">
         <f t="shared" si="9"/>
-        <v>994</v>
-      </c>
-      <c r="F160" s="148">
-        <f t="shared" si="10"/>
-        <v>3.7110322941945162E-2</v>
-      </c>
-    </row>
-    <row r="161" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>-0.57658202718799045</v>
+      </c>
+    </row>
+    <row r="161" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B161" s="82" t="s">
         <v>65</v>
       </c>
       <c r="C161" s="38">
-        <v>2642</v>
+        <v>4092</v>
       </c>
       <c r="D161" s="38">
-        <v>2118</v>
+        <v>1027</v>
       </c>
       <c r="E161" s="38">
+        <f t="shared" si="8"/>
+        <v>-3065</v>
+      </c>
+      <c r="F161" s="144">
         <f t="shared" si="9"/>
-        <v>-524</v>
-      </c>
-      <c r="F161" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.19833459500378503</v>
-      </c>
-    </row>
-    <row r="162" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>-0.74902248289345064</v>
+      </c>
+      <c r="H161" s="93"/>
+      <c r="I161" s="93"/>
+    </row>
+    <row r="162" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B162" s="82" t="s">
         <v>69</v>
       </c>
       <c r="C162" s="38">
-        <v>689</v>
+        <v>747</v>
       </c>
       <c r="D162" s="38">
-        <v>833</v>
+        <v>251</v>
       </c>
       <c r="E162" s="38">
+        <f t="shared" si="8"/>
+        <v>-496</v>
+      </c>
+      <c r="F162" s="144">
         <f t="shared" si="9"/>
-        <v>144</v>
-      </c>
-      <c r="F162" s="144">
-        <f t="shared" si="10"/>
-        <v>0.20899854862119005</v>
-      </c>
-    </row>
-    <row r="163" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>-0.66398929049531463</v>
+      </c>
+    </row>
+    <row r="163" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B163" s="88" t="s">
         <v>76</v>
       </c>
       <c r="C163" s="38">
-        <v>2450</v>
+        <v>3398</v>
       </c>
       <c r="D163" s="38">
-        <v>2249</v>
+        <v>1804</v>
       </c>
       <c r="E163" s="38">
+        <f t="shared" si="8"/>
+        <v>-1594</v>
+      </c>
+      <c r="F163" s="144">
         <f t="shared" si="9"/>
-        <v>-201</v>
-      </c>
-      <c r="F163" s="144">
-        <f t="shared" si="10"/>
-        <v>-8.2040816326530597E-2</v>
-      </c>
-    </row>
-    <row r="164" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>-0.46909947027663335</v>
+      </c>
+      <c r="H163" s="93"/>
+      <c r="I163" s="93"/>
+      <c r="J163" s="66"/>
+    </row>
+    <row r="164" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B164" s="89" t="s">
         <v>79</v>
       </c>
       <c r="C164" s="38">
-        <v>589</v>
+        <v>1535</v>
       </c>
       <c r="D164" s="38">
-        <v>622</v>
+        <v>1005</v>
       </c>
       <c r="E164" s="38">
+        <f t="shared" si="8"/>
+        <v>-530</v>
+      </c>
+      <c r="F164" s="144">
         <f t="shared" si="9"/>
-        <v>33</v>
-      </c>
-      <c r="F164" s="144">
-        <f t="shared" si="10"/>
-        <v>5.6027164685908293E-2</v>
-      </c>
-    </row>
-    <row r="165" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>-0.34527687296416942</v>
+      </c>
+    </row>
+    <row r="165" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B165" s="89" t="s">
         <v>88</v>
       </c>
       <c r="C165" s="38">
-        <v>715</v>
+        <v>882</v>
       </c>
       <c r="D165" s="38">
-        <v>359</v>
+        <v>229</v>
       </c>
       <c r="E165" s="38">
+        <f t="shared" si="8"/>
+        <v>-653</v>
+      </c>
+      <c r="F165" s="144">
         <f t="shared" si="9"/>
-        <v>-356</v>
-      </c>
-      <c r="F165" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.49790209790209794</v>
-      </c>
-    </row>
-    <row r="166" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>-0.74036281179138319</v>
+      </c>
+    </row>
+    <row r="166" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B166" s="89" t="s">
         <v>91</v>
       </c>
       <c r="C166" s="38">
-        <v>4105</v>
+        <v>9463</v>
       </c>
       <c r="D166" s="38">
-        <v>4772</v>
+        <v>6291</v>
       </c>
       <c r="E166" s="38">
+        <f t="shared" si="8"/>
+        <v>-3172</v>
+      </c>
+      <c r="F166" s="144">
         <f t="shared" si="9"/>
-        <v>667</v>
-      </c>
-      <c r="F166" s="144">
-        <f t="shared" si="10"/>
-        <v>0.16248477466504263</v>
-      </c>
-    </row>
-    <row r="167" spans="2:6" ht="12" x14ac:dyDescent="0.2">
+        <v>-0.33520025361935957</v>
+      </c>
+    </row>
+    <row r="167" spans="2:10" ht="12" x14ac:dyDescent="0.2">
       <c r="B167" s="81" t="s">
         <v>96</v>
       </c>
       <c r="C167" s="38">
-        <v>391</v>
+        <v>454</v>
       </c>
       <c r="D167" s="38">
-        <v>362</v>
+        <v>126</v>
       </c>
       <c r="E167" s="38">
+        <f t="shared" si="8"/>
+        <v>-328</v>
+      </c>
+      <c r="F167" s="144">
         <f t="shared" si="9"/>
-        <v>-29</v>
-      </c>
-      <c r="F167" s="144">
-        <f t="shared" si="10"/>
-        <v>-7.4168797953964249E-2</v>
-      </c>
-    </row>
-    <row r="168" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>-0.72246696035242297</v>
+      </c>
+    </row>
+    <row r="168" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B168" s="81" t="s">
         <v>103</v>
       </c>
       <c r="C168" s="38">
-        <v>2631</v>
+        <v>2727</v>
       </c>
       <c r="D168" s="38">
-        <v>3083</v>
+        <v>1842</v>
       </c>
       <c r="E168" s="38">
+        <f t="shared" si="8"/>
+        <v>-885</v>
+      </c>
+      <c r="F168" s="144">
         <f t="shared" si="9"/>
-        <v>452</v>
-      </c>
-      <c r="F168" s="144">
-        <f t="shared" si="10"/>
-        <v>0.1717977955150134</v>
-      </c>
-    </row>
-    <row r="169" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>-0.32453245324532454</v>
+      </c>
+    </row>
+    <row r="169" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B169" s="81" t="s">
         <v>157</v>
       </c>
       <c r="C169" s="38">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D169" s="38">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E169" s="38">
+        <f t="shared" si="8"/>
+        <v>14</v>
+      </c>
+      <c r="F169" s="144">
         <f t="shared" si="9"/>
-        <v>24</v>
-      </c>
-      <c r="F169" s="144">
-        <f t="shared" si="10"/>
-        <v>1.263157894736842</v>
-      </c>
-    </row>
-    <row r="170" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="170" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B170" s="81" t="s">
         <v>117</v>
       </c>
       <c r="C170" s="38">
-        <v>452</v>
+        <v>1630</v>
       </c>
       <c r="D170" s="38">
-        <v>457</v>
+        <v>255</v>
       </c>
       <c r="E170" s="38">
+        <f t="shared" si="8"/>
+        <v>-1375</v>
+      </c>
+      <c r="F170" s="144">
         <f t="shared" si="9"/>
-        <v>5</v>
-      </c>
-      <c r="F170" s="144">
-        <f t="shared" si="10"/>
-        <v>1.106194690265494E-2</v>
-      </c>
-    </row>
-    <row r="171" spans="2:6" ht="12" x14ac:dyDescent="0.2">
+        <v>-0.84355828220858897</v>
+      </c>
+    </row>
+    <row r="171" spans="2:10" ht="12" x14ac:dyDescent="0.2">
       <c r="B171" s="81" t="s">
         <v>126</v>
       </c>
       <c r="C171" s="38">
-        <v>6500</v>
+        <v>20410</v>
       </c>
       <c r="D171" s="38">
-        <v>8862</v>
+        <v>7701</v>
       </c>
       <c r="E171" s="38">
+        <f t="shared" si="8"/>
+        <v>-12709</v>
+      </c>
+      <c r="F171" s="144">
         <f t="shared" si="9"/>
-        <v>2362</v>
-      </c>
-      <c r="F171" s="144">
-        <f t="shared" si="10"/>
-        <v>0.36338461538461542</v>
-      </c>
-    </row>
-    <row r="172" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>-0.62268495835374815</v>
+      </c>
+    </row>
+    <row r="172" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B172" s="82" t="s">
         <v>134</v>
       </c>
       <c r="C172" s="38">
-        <v>1596</v>
+        <v>2104</v>
       </c>
       <c r="D172" s="38">
-        <v>764</v>
+        <v>668</v>
       </c>
       <c r="E172" s="38">
+        <f t="shared" si="8"/>
+        <v>-1436</v>
+      </c>
+      <c r="F172" s="144">
         <f t="shared" si="9"/>
-        <v>-832</v>
-      </c>
-      <c r="F172" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.52130325814536338</v>
-      </c>
-    </row>
-    <row r="173" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>-0.68250950570342206</v>
+      </c>
+    </row>
+    <row r="173" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B173" s="81" t="s">
         <v>147</v>
       </c>
       <c r="C173" s="38">
-        <v>4006</v>
+        <v>5417</v>
       </c>
       <c r="D173" s="38">
-        <v>3255</v>
+        <v>1150</v>
       </c>
       <c r="E173" s="38">
+        <f t="shared" si="8"/>
+        <v>-4267</v>
+      </c>
+      <c r="F173" s="144">
         <f t="shared" si="9"/>
-        <v>-751</v>
-      </c>
-      <c r="F173" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.18746879680479278</v>
-      </c>
-    </row>
-    <row r="174" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>-0.7877053719771091</v>
+      </c>
+    </row>
+    <row r="174" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B174" s="86" t="s">
         <v>204</v>
       </c>
       <c r="C174" s="53">
-        <v>4428</v>
+        <v>3760</v>
       </c>
       <c r="D174" s="53">
-        <v>3625</v>
+        <v>2517</v>
       </c>
       <c r="E174" s="53">
+        <f t="shared" si="8"/>
+        <v>-1243</v>
+      </c>
+      <c r="F174" s="146">
         <f t="shared" si="9"/>
-        <v>-803</v>
-      </c>
-      <c r="F174" s="146">
-        <f t="shared" si="10"/>
-        <v>-0.18134598012646796</v>
-      </c>
-    </row>
-    <row r="175" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>-0.33058510638297878</v>
+      </c>
+    </row>
+    <row r="175" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B175" s="80" t="s">
         <v>205</v>
       </c>
       <c r="C175" s="51">
-        <v>737</v>
+        <v>687</v>
       </c>
       <c r="D175" s="52">
-        <v>425</v>
+        <v>329</v>
       </c>
       <c r="E175" s="51">
+        <f t="shared" si="8"/>
+        <v>-358</v>
+      </c>
+      <c r="F175" s="143">
         <f t="shared" si="9"/>
-        <v>-312</v>
-      </c>
-      <c r="F175" s="143">
-        <f t="shared" si="10"/>
-        <v>-0.42333785617367703</v>
-      </c>
-    </row>
-    <row r="176" spans="2:6" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>-0.5211062590975255</v>
+      </c>
+    </row>
+    <row r="176" spans="2:10" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B176" s="85" t="s">
         <v>168</v>
       </c>
       <c r="C176" s="38">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D176" s="38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E176" s="38">
+        <f t="shared" si="8"/>
+        <v>-8</v>
+      </c>
+      <c r="F176" s="144">
         <f t="shared" si="9"/>
-        <v>3</v>
-      </c>
-      <c r="F176" s="144">
-        <f t="shared" si="10"/>
-        <v>3</v>
+        <v>-0.72727272727272729</v>
       </c>
     </row>
     <row r="177" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6490,18 +6516,18 @@
         <v>77</v>
       </c>
       <c r="C177" s="38">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D177" s="38">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E177" s="38">
+        <f t="shared" si="8"/>
+        <v>-82</v>
+      </c>
+      <c r="F177" s="144">
         <f t="shared" si="9"/>
-        <v>-62</v>
-      </c>
-      <c r="F177" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.54867256637168138</v>
+        <v>-0.68907563025210083</v>
       </c>
     </row>
     <row r="178" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6509,18 +6535,18 @@
         <v>161</v>
       </c>
       <c r="C178" s="38">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D178" s="38">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E178" s="38">
+        <f t="shared" si="8"/>
+        <v>-24</v>
+      </c>
+      <c r="F178" s="144">
         <f t="shared" si="9"/>
-        <v>-27</v>
-      </c>
-      <c r="F178" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.67500000000000004</v>
+        <v>-0.63157894736842102</v>
       </c>
     </row>
     <row r="179" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6528,18 +6554,18 @@
         <v>84</v>
       </c>
       <c r="C179" s="38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D179" s="38">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E179" s="38">
+        <f t="shared" si="8"/>
+        <v>-3</v>
+      </c>
+      <c r="F179" s="144">
         <f t="shared" si="9"/>
-        <v>-4</v>
-      </c>
-      <c r="F179" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.5</v>
+        <v>-0.33333333333333337</v>
       </c>
     </row>
     <row r="180" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6547,18 +6573,18 @@
         <v>85</v>
       </c>
       <c r="C180" s="38">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="D180" s="38">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="E180" s="38">
+        <f t="shared" si="8"/>
+        <v>-13</v>
+      </c>
+      <c r="F180" s="144">
         <f t="shared" si="9"/>
-        <v>-8</v>
-      </c>
-      <c r="F180" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.11111111111111116</v>
+        <v>-0.29545454545454541</v>
       </c>
     </row>
     <row r="181" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6566,18 +6592,18 @@
         <v>97</v>
       </c>
       <c r="C181" s="38">
-        <v>194</v>
+        <v>136</v>
       </c>
       <c r="D181" s="38">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="E181" s="38">
+        <f t="shared" si="8"/>
+        <v>-59</v>
+      </c>
+      <c r="F181" s="144">
         <f t="shared" si="9"/>
-        <v>-94</v>
-      </c>
-      <c r="F181" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.48453608247422686</v>
+        <v>-0.43382352941176472</v>
       </c>
     </row>
     <row r="182" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6585,18 +6611,18 @@
         <v>188</v>
       </c>
       <c r="C182" s="38">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="D182" s="38">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="E182" s="38">
+        <f t="shared" si="8"/>
+        <v>-126</v>
+      </c>
+      <c r="F182" s="144">
         <f t="shared" si="9"/>
-        <v>-36</v>
-      </c>
-      <c r="F182" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.3214285714285714</v>
+        <v>-0.85714285714285721</v>
       </c>
     </row>
     <row r="183" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6604,18 +6630,18 @@
         <v>105</v>
       </c>
       <c r="C183" s="38">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D183" s="38">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E183" s="38">
+        <f t="shared" si="8"/>
+        <v>-1</v>
+      </c>
+      <c r="F183" s="144">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F183" s="144">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <v>-8.333333333333337E-2</v>
       </c>
     </row>
     <row r="184" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6623,18 +6649,18 @@
         <v>106</v>
       </c>
       <c r="C184" s="38">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D184" s="38">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E184" s="38">
+        <f t="shared" si="8"/>
+        <v>-4</v>
+      </c>
+      <c r="F184" s="144">
         <f t="shared" si="9"/>
-        <v>-16</v>
-      </c>
-      <c r="F184" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.45714285714285718</v>
+        <v>-0.11764705882352944</v>
       </c>
     </row>
     <row r="185" spans="2:6" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6648,7 +6674,7 @@
         <v>0</v>
       </c>
       <c r="E185" s="38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F185" s="144"/>
@@ -6658,18 +6684,18 @@
         <v>182</v>
       </c>
       <c r="C186" s="38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D186" s="38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E186" s="38">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="F186" s="144">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F186" s="144">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6677,18 +6703,18 @@
         <v>112</v>
       </c>
       <c r="C187" s="38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D187" s="38">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E187" s="38">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F187" s="144">
         <f t="shared" si="9"/>
-        <v>8</v>
-      </c>
-      <c r="F187" s="144">
-        <f t="shared" si="10"/>
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="2:6" ht="12" x14ac:dyDescent="0.2">
@@ -6702,7 +6728,7 @@
         <v>0</v>
       </c>
       <c r="E188" s="38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F188" s="144"/>
@@ -6712,18 +6738,18 @@
         <v>123</v>
       </c>
       <c r="C189" s="38">
+        <v>14</v>
+      </c>
+      <c r="D189" s="38">
         <v>5</v>
       </c>
-      <c r="D189" s="38">
-        <v>3</v>
-      </c>
       <c r="E189" s="38">
+        <f t="shared" si="8"/>
+        <v>-9</v>
+      </c>
+      <c r="F189" s="144">
         <f t="shared" si="9"/>
-        <v>-2</v>
-      </c>
-      <c r="F189" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.4</v>
+        <v>-0.64285714285714279</v>
       </c>
     </row>
     <row r="190" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6731,18 +6757,18 @@
         <v>128</v>
       </c>
       <c r="C190" s="38">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D190" s="38">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E190" s="38">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="F190" s="144">
         <f t="shared" si="9"/>
-        <v>-7</v>
-      </c>
-      <c r="F190" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.46666666666666667</v>
+        <v>0.19999999999999996</v>
       </c>
     </row>
     <row r="191" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6750,18 +6776,18 @@
         <v>135</v>
       </c>
       <c r="C191" s="38">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D191" s="38">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E191" s="38">
+        <f t="shared" si="8"/>
+        <v>-24</v>
+      </c>
+      <c r="F191" s="144">
         <f t="shared" si="9"/>
-        <v>-35</v>
-      </c>
-      <c r="F191" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.63636363636363635</v>
+        <v>-0.46153846153846156</v>
       </c>
     </row>
     <row r="192" spans="2:6" ht="12" x14ac:dyDescent="0.2">
@@ -6769,18 +6795,18 @@
         <v>177</v>
       </c>
       <c r="C192" s="38">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D192" s="38">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E192" s="38">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="F192" s="144">
         <f t="shared" si="9"/>
-        <v>-11</v>
-      </c>
-      <c r="F192" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.43999999999999995</v>
+        <v>0.16666666666666674</v>
       </c>
     </row>
     <row r="193" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6788,18 +6814,18 @@
         <v>144</v>
       </c>
       <c r="C193" s="38">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D193" s="38">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E193" s="38">
+        <f t="shared" si="8"/>
+        <v>-12</v>
+      </c>
+      <c r="F193" s="144">
         <f t="shared" si="9"/>
-        <v>-23</v>
-      </c>
-      <c r="F193" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.46938775510204078</v>
+        <v>-0.30000000000000004</v>
       </c>
     </row>
     <row r="194" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6807,18 +6833,18 @@
         <v>180</v>
       </c>
       <c r="C194" s="38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D194" s="38">
         <v>4</v>
       </c>
       <c r="E194" s="38">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F194" s="144">
         <f t="shared" si="9"/>
-        <v>2</v>
-      </c>
-      <c r="F194" s="144">
-        <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6827,18 +6853,18 @@
         <v>206</v>
       </c>
       <c r="C195" s="56">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="D195" s="52">
-        <v>334</v>
+        <v>302</v>
       </c>
       <c r="E195" s="56">
+        <f t="shared" si="8"/>
+        <v>-36</v>
+      </c>
+      <c r="F195" s="147">
         <f t="shared" si="9"/>
-        <v>-17</v>
-      </c>
-      <c r="F195" s="147">
-        <f t="shared" si="10"/>
-        <v>-4.8433048433048409E-2</v>
+        <v>-0.10650887573964496</v>
       </c>
     </row>
     <row r="196" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6850,15 +6876,15 @@
         <v>2</v>
       </c>
       <c r="D196" s="38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E196" s="38">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="F196" s="144">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F196" s="144">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="197" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6867,18 +6893,18 @@
         <v>183</v>
       </c>
       <c r="C197" s="38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D197" s="38">
         <v>2</v>
       </c>
       <c r="E197" s="38">
+        <f t="shared" si="8"/>
+        <v>-3</v>
+      </c>
+      <c r="F197" s="144">
         <f t="shared" si="9"/>
-        <v>-2</v>
-      </c>
-      <c r="F197" s="144">
-        <f t="shared" si="10"/>
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="198" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6887,18 +6913,18 @@
         <v>170</v>
       </c>
       <c r="C198" s="38">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D198" s="38">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E198" s="38">
-        <f t="shared" ref="E198:E234" si="11">D198-C198</f>
-        <v>1</v>
+        <f t="shared" ref="E198:E234" si="10">D198-C198</f>
+        <v>4</v>
       </c>
       <c r="F198" s="144">
-        <f t="shared" ref="F198:F234" si="12">D198/C198-1</f>
-        <v>0.5</v>
+        <f t="shared" ref="F198:F234" si="11">D198/C198-1</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="199" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6907,18 +6933,18 @@
         <v>72</v>
       </c>
       <c r="C199" s="38">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="D199" s="38">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E199" s="38">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="F199" s="144">
         <f t="shared" si="11"/>
-        <v>-36</v>
-      </c>
-      <c r="F199" s="144">
-        <f t="shared" si="12"/>
-        <v>-0.50704225352112675</v>
+        <v>7.6923076923076872E-2</v>
       </c>
     </row>
     <row r="200" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6930,15 +6956,15 @@
         <v>2</v>
       </c>
       <c r="D200" s="38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E200" s="38">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="F200" s="144">
         <f t="shared" si="11"/>
-        <v>-2</v>
-      </c>
-      <c r="F200" s="144">
-        <f t="shared" si="12"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6947,18 +6973,18 @@
         <v>156</v>
       </c>
       <c r="C201" s="38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D201" s="38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E201" s="38">
+        <f t="shared" si="10"/>
+        <v>-2</v>
+      </c>
+      <c r="F201" s="144">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="F201" s="144">
-        <f t="shared" si="12"/>
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="202" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6967,16 +6993,19 @@
         <v>93</v>
       </c>
       <c r="C202" s="38">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D202" s="38">
         <v>0</v>
       </c>
       <c r="E202" s="38">
+        <f t="shared" si="10"/>
+        <v>-9</v>
+      </c>
+      <c r="F202" s="144">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F202" s="144"/>
+        <v>-1</v>
+      </c>
     </row>
     <row r="203" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="11"/>
@@ -6984,18 +7013,18 @@
         <v>101</v>
       </c>
       <c r="C203" s="38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D203" s="38">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E203" s="38">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="F203" s="144">
         <f t="shared" si="11"/>
-        <v>2</v>
-      </c>
-      <c r="F203" s="144">
-        <f t="shared" si="12"/>
-        <v>0.33333333333333326</v>
+        <v>0.19999999999999996</v>
       </c>
     </row>
     <row r="204" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7004,18 +7033,18 @@
         <v>104</v>
       </c>
       <c r="C204" s="38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D204" s="38">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E204" s="38">
+        <f t="shared" si="10"/>
+        <v>-1</v>
+      </c>
+      <c r="F204" s="144">
         <f t="shared" si="11"/>
-        <v>-5</v>
-      </c>
-      <c r="F204" s="144">
-        <f t="shared" si="12"/>
-        <v>-1</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="205" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7024,18 +7053,18 @@
         <v>172</v>
       </c>
       <c r="C205" s="38">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D205" s="38">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E205" s="38">
+        <f t="shared" si="10"/>
+        <v>-7</v>
+      </c>
+      <c r="F205" s="144">
         <f t="shared" si="11"/>
-        <v>5</v>
-      </c>
-      <c r="F205" s="144">
-        <f t="shared" si="12"/>
-        <v>0.71428571428571419</v>
+        <v>-0.38888888888888884</v>
       </c>
     </row>
     <row r="206" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7044,18 +7073,18 @@
         <v>158</v>
       </c>
       <c r="C206" s="38">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D206" s="38">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E206" s="38">
+        <f t="shared" si="10"/>
+        <v>-9</v>
+      </c>
+      <c r="F206" s="144">
         <f t="shared" si="11"/>
-        <v>8</v>
-      </c>
-      <c r="F206" s="144">
-        <f t="shared" si="12"/>
-        <v>1.1428571428571428</v>
+        <v>-0.52941176470588236</v>
       </c>
     </row>
     <row r="207" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7064,18 +7093,18 @@
         <v>163</v>
       </c>
       <c r="C207" s="38">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D207" s="38">
+        <v>4</v>
+      </c>
+      <c r="E207" s="38">
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="E207" s="38">
+      <c r="F207" s="144">
         <f t="shared" si="11"/>
-        <v>-7</v>
-      </c>
-      <c r="F207" s="144">
-        <f t="shared" si="12"/>
-        <v>-0.875</v>
+        <v>0.33333333333333326</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7084,18 +7113,18 @@
         <v>115</v>
       </c>
       <c r="C208" s="38">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D208" s="38">
-        <v>240</v>
+        <v>204</v>
       </c>
       <c r="E208" s="38">
+        <f t="shared" si="10"/>
+        <v>-12</v>
+      </c>
+      <c r="F208" s="144">
         <f t="shared" si="11"/>
-        <v>14</v>
-      </c>
-      <c r="F208" s="144">
-        <f t="shared" si="12"/>
-        <v>6.1946902654867353E-2</v>
+        <v>-5.555555555555558E-2</v>
       </c>
     </row>
     <row r="209" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7104,18 +7133,18 @@
         <v>129</v>
       </c>
       <c r="C209" s="38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D209" s="38">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E209" s="38">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="F209" s="144">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="F209" s="144">
-        <f t="shared" si="12"/>
-        <v>0.19999999999999996</v>
+        <v>0.14285714285714279</v>
       </c>
     </row>
     <row r="210" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7124,18 +7153,18 @@
         <v>132</v>
       </c>
       <c r="C210" s="38">
+        <v>8</v>
+      </c>
+      <c r="D210" s="38">
         <v>3</v>
       </c>
-      <c r="D210" s="38">
-        <v>4</v>
-      </c>
       <c r="E210" s="38">
+        <f t="shared" si="10"/>
+        <v>-5</v>
+      </c>
+      <c r="F210" s="144">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="F210" s="144">
-        <f t="shared" si="12"/>
-        <v>0.33333333333333326</v>
+        <v>-0.625</v>
       </c>
     </row>
     <row r="211" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7143,18 +7172,18 @@
         <v>192</v>
       </c>
       <c r="C211" s="38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D211" s="38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E211" s="38">
+        <f t="shared" si="10"/>
+        <v>-1</v>
+      </c>
+      <c r="F211" s="144">
         <f t="shared" si="11"/>
-        <v>2</v>
-      </c>
-      <c r="F211" s="144">
-        <f t="shared" si="12"/>
-        <v>1</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="212" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7162,18 +7191,18 @@
         <v>125</v>
       </c>
       <c r="C212" s="56">
-        <v>1099</v>
+        <v>846</v>
       </c>
       <c r="D212" s="52">
-        <v>1202</v>
+        <v>694</v>
       </c>
       <c r="E212" s="56">
+        <f t="shared" si="10"/>
+        <v>-152</v>
+      </c>
+      <c r="F212" s="147">
         <f t="shared" si="11"/>
-        <v>103</v>
-      </c>
-      <c r="F212" s="147">
-        <f t="shared" si="12"/>
-        <v>9.3721565059144751E-2</v>
+        <v>-0.17966903073286056</v>
       </c>
     </row>
     <row r="213" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7182,18 +7211,18 @@
         <v>167</v>
       </c>
       <c r="C213" s="38">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D213" s="38">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E213" s="38">
+        <f t="shared" si="10"/>
+        <v>6</v>
+      </c>
+      <c r="F213" s="144">
         <f t="shared" si="11"/>
-        <v>15</v>
-      </c>
-      <c r="F213" s="144">
-        <f t="shared" si="12"/>
-        <v>2.1428571428571428</v>
+        <v>3</v>
       </c>
     </row>
     <row r="214" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7202,16 +7231,19 @@
         <v>194</v>
       </c>
       <c r="C214" s="38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D214" s="38">
         <v>0</v>
       </c>
       <c r="E214" s="38">
+        <f t="shared" si="10"/>
+        <v>-1</v>
+      </c>
+      <c r="F214" s="144">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F214" s="144"/>
+        <v>-1</v>
+      </c>
     </row>
     <row r="215" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="11"/>
@@ -7219,18 +7251,18 @@
         <v>159</v>
       </c>
       <c r="C215" s="38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D215" s="38">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E215" s="38">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="F215" s="144">
         <f t="shared" si="11"/>
-        <v>-7</v>
-      </c>
-      <c r="F215" s="144">
-        <f t="shared" si="12"/>
-        <v>-0.875</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="216" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7238,18 +7270,18 @@
         <v>125</v>
       </c>
       <c r="C216" s="38">
-        <v>1084</v>
+        <v>834</v>
       </c>
       <c r="D216" s="38">
-        <v>1178</v>
+        <v>671</v>
       </c>
       <c r="E216" s="38">
+        <f t="shared" si="10"/>
+        <v>-163</v>
+      </c>
+      <c r="F216" s="144">
         <f t="shared" si="11"/>
-        <v>94</v>
-      </c>
-      <c r="F216" s="144">
-        <f t="shared" si="12"/>
-        <v>8.6715867158671633E-2</v>
+        <v>-0.19544364508393286</v>
       </c>
     </row>
     <row r="217" spans="1:6" ht="12" x14ac:dyDescent="0.2">
@@ -7257,30 +7289,33 @@
         <v>184</v>
       </c>
       <c r="C217" s="38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D217" s="38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E217" s="38">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="F217" s="144">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="F217" s="144"/>
     </row>
     <row r="218" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B218" s="80" t="s">
         <v>207</v>
       </c>
       <c r="C218" s="56">
-        <v>2151</v>
+        <v>1834</v>
       </c>
       <c r="D218" s="52">
-        <v>1621</v>
+        <v>1152</v>
       </c>
       <c r="E218" s="56">
-        <f t="shared" si="11"/>
-        <v>-530</v>
+        <f t="shared" si="10"/>
+        <v>-682</v>
       </c>
       <c r="F218" s="147"/>
     </row>
@@ -7289,18 +7324,18 @@
         <v>62</v>
       </c>
       <c r="C219" s="38">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="D219" s="38">
-        <v>305</v>
+        <v>207</v>
       </c>
       <c r="E219" s="38">
+        <f t="shared" si="10"/>
+        <v>-90</v>
+      </c>
+      <c r="F219" s="144">
         <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="F219" s="144">
-        <f t="shared" si="12"/>
-        <v>3.2894736842106198E-3</v>
+        <v>-0.30303030303030298</v>
       </c>
     </row>
     <row r="220" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7308,18 +7343,18 @@
         <v>108</v>
       </c>
       <c r="C220" s="38">
-        <v>475</v>
+        <v>403</v>
       </c>
       <c r="D220" s="38">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E220" s="38">
+        <f t="shared" si="10"/>
+        <v>-122</v>
+      </c>
+      <c r="F220" s="144">
         <f t="shared" si="11"/>
-        <v>-186</v>
-      </c>
-      <c r="F220" s="144">
-        <f t="shared" si="12"/>
-        <v>-0.39157894736842103</v>
+        <v>-0.30272952853598012</v>
       </c>
     </row>
     <row r="221" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7327,18 +7362,18 @@
         <v>136</v>
       </c>
       <c r="C221" s="38">
-        <v>986</v>
+        <v>799</v>
       </c>
       <c r="D221" s="38">
-        <v>644</v>
+        <v>376</v>
       </c>
       <c r="E221" s="38">
+        <f t="shared" si="10"/>
+        <v>-423</v>
+      </c>
+      <c r="F221" s="144">
         <f t="shared" si="11"/>
-        <v>-342</v>
-      </c>
-      <c r="F221" s="144">
-        <f t="shared" si="12"/>
-        <v>-0.34685598377281945</v>
+        <v>-0.52941176470588236</v>
       </c>
     </row>
     <row r="222" spans="1:6" ht="12" x14ac:dyDescent="0.2">
@@ -7346,18 +7381,18 @@
         <v>143</v>
       </c>
       <c r="C222" s="38">
-        <v>386</v>
+        <v>335</v>
       </c>
       <c r="D222" s="38">
-        <v>383</v>
+        <v>288</v>
       </c>
       <c r="E222" s="38">
+        <f t="shared" si="10"/>
+        <v>-47</v>
+      </c>
+      <c r="F222" s="144">
         <f t="shared" si="11"/>
-        <v>-3</v>
-      </c>
-      <c r="F222" s="144">
-        <f t="shared" si="12"/>
-        <v>-7.7720207253886286E-3</v>
+        <v>-0.14029850746268657</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.2">
@@ -7365,18 +7400,18 @@
         <v>208</v>
       </c>
       <c r="C223" s="56">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="D223" s="52">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E223" s="56">
+        <f t="shared" si="10"/>
+        <v>-15</v>
+      </c>
+      <c r="F223" s="147">
         <f t="shared" si="11"/>
-        <v>-47</v>
-      </c>
-      <c r="F223" s="147">
-        <f t="shared" si="12"/>
-        <v>-0.52222222222222214</v>
+        <v>-0.27272727272727271</v>
       </c>
     </row>
     <row r="224" spans="1:6" ht="12" x14ac:dyDescent="0.2">
@@ -7384,18 +7419,18 @@
         <v>153</v>
       </c>
       <c r="C224" s="38">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D224" s="38">
         <v>6</v>
       </c>
       <c r="E224" s="38">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="F224" s="144">
         <f t="shared" si="11"/>
-        <v>-9</v>
-      </c>
-      <c r="F224" s="144">
-        <f t="shared" si="12"/>
-        <v>-0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="225" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7403,17 +7438,17 @@
         <v>169</v>
       </c>
       <c r="C225" s="38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D225" s="38">
         <v>0</v>
       </c>
       <c r="E225" s="38">
+        <f t="shared" si="10"/>
+        <v>-1</v>
+      </c>
+      <c r="F225" s="144">
         <f t="shared" si="11"/>
-        <v>-2</v>
-      </c>
-      <c r="F225" s="144">
-        <f t="shared" si="12"/>
         <v>-1</v>
       </c>
     </row>
@@ -7422,18 +7457,18 @@
         <v>94</v>
       </c>
       <c r="C226" s="38">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="D226" s="38">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E226" s="38">
+        <f t="shared" si="10"/>
+        <v>-9</v>
+      </c>
+      <c r="F226" s="144">
         <f t="shared" si="11"/>
-        <v>-17</v>
-      </c>
-      <c r="F226" s="144">
-        <f t="shared" si="12"/>
-        <v>-0.36956521739130432</v>
+        <v>-0.28125</v>
       </c>
     </row>
     <row r="227" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7441,19 +7476,16 @@
         <v>98</v>
       </c>
       <c r="C227" s="38">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D227" s="38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E227" s="38">
-        <f t="shared" si="11"/>
-        <v>-6</v>
-      </c>
-      <c r="F227" s="144">
-        <f t="shared" si="12"/>
-        <v>-0.6</v>
-      </c>
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="F227" s="144"/>
     </row>
     <row r="228" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B228" s="85" t="s">
@@ -7466,7 +7498,7 @@
         <v>0</v>
       </c>
       <c r="E228" s="38">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F228" s="144"/>
@@ -7476,18 +7508,18 @@
         <v>193</v>
       </c>
       <c r="C229" s="38">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D229" s="38">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E229" s="38">
+        <f t="shared" si="10"/>
+        <v>-9</v>
+      </c>
+      <c r="F229" s="144">
         <f t="shared" si="11"/>
-        <v>-12</v>
-      </c>
-      <c r="F229" s="144">
-        <f t="shared" si="12"/>
-        <v>-0.75</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="230" spans="1:6" s="9" customFormat="1" ht="12" x14ac:dyDescent="0.2">
@@ -7495,37 +7527,34 @@
         <v>231</v>
       </c>
       <c r="C230" s="38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D230" s="38">
         <v>0</v>
       </c>
       <c r="E230" s="38">
-        <f t="shared" si="11"/>
-        <v>-1</v>
-      </c>
-      <c r="F230" s="144">
-        <f t="shared" si="12"/>
-        <v>-1</v>
-      </c>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F230" s="144"/>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B231" s="86" t="s">
         <v>137</v>
       </c>
       <c r="C231" s="53">
-        <v>106491</v>
+        <v>98545</v>
       </c>
       <c r="D231" s="53">
-        <v>109066</v>
+        <v>100281</v>
       </c>
       <c r="E231" s="53">
+        <f t="shared" si="10"/>
+        <v>1736</v>
+      </c>
+      <c r="F231" s="146">
         <f t="shared" si="11"/>
-        <v>2575</v>
-      </c>
-      <c r="F231" s="146">
-        <f t="shared" si="12"/>
-        <v>2.4180447173939523E-2</v>
+        <v>1.7616317418438276E-2</v>
       </c>
     </row>
     <row r="232" spans="1:6" ht="12" x14ac:dyDescent="0.2">
@@ -7533,18 +7562,18 @@
         <v>254</v>
       </c>
       <c r="C232" s="38">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="D232" s="38">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E232" s="38">
+        <f t="shared" si="10"/>
+        <v>-60</v>
+      </c>
+      <c r="F232" s="144">
         <f t="shared" si="11"/>
-        <v>-14</v>
-      </c>
-      <c r="F232" s="144">
-        <f t="shared" si="12"/>
-        <v>-0.17721518987341767</v>
+        <v>-0.45112781954887216</v>
       </c>
     </row>
     <row r="233" spans="1:6" s="20" customFormat="1" ht="12" x14ac:dyDescent="0.2">
@@ -7552,18 +7581,18 @@
         <v>285</v>
       </c>
       <c r="C233" s="38">
-        <v>104775</v>
+        <v>96293</v>
       </c>
       <c r="D233" s="38">
-        <v>107685</v>
+        <v>98872</v>
       </c>
       <c r="E233" s="38">
+        <f t="shared" si="10"/>
+        <v>2579</v>
+      </c>
+      <c r="F233" s="144">
         <f t="shared" si="11"/>
-        <v>2910</v>
-      </c>
-      <c r="F233" s="144">
-        <f t="shared" si="12"/>
-        <v>2.7773801002147547E-2</v>
+        <v>2.6782839874134101E-2</v>
       </c>
     </row>
     <row r="234" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -7571,18 +7600,18 @@
         <v>137</v>
       </c>
       <c r="C234" s="91">
-        <v>1637</v>
+        <v>2119</v>
       </c>
       <c r="D234" s="91">
-        <v>1316</v>
+        <v>1336</v>
       </c>
       <c r="E234" s="91">
+        <f t="shared" si="10"/>
+        <v>-783</v>
+      </c>
+      <c r="F234" s="149">
         <f t="shared" si="11"/>
-        <v>-321</v>
-      </c>
-      <c r="F234" s="149">
-        <f t="shared" si="12"/>
-        <v>-0.19609040928527799</v>
+        <v>-0.36951392166116093</v>
       </c>
     </row>
     <row r="236" spans="1:6" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7591,12 +7620,12 @@
       <c r="F236" s="66"/>
     </row>
     <row r="238" spans="1:6" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B238" s="152" t="s">
+      <c r="B238" s="154" t="s">
         <v>209</v>
       </c>
-      <c r="C238" s="153"/>
-      <c r="D238" s="153"/>
-      <c r="E238" s="153"/>
+      <c r="C238" s="155"/>
+      <c r="D238" s="155"/>
+      <c r="E238" s="155"/>
       <c r="F238" s="66"/>
     </row>
     <row r="239" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7643,14 +7672,14 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="155" t="s">
+      <c r="B2" s="157" t="s">
         <v>249</v>
       </c>
-      <c r="C2" s="156"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156"/>
-      <c r="F2" s="156"/>
-      <c r="G2" s="156"/>
+      <c r="C2" s="158"/>
+      <c r="D2" s="158"/>
+      <c r="E2" s="158"/>
+      <c r="F2" s="158"/>
+      <c r="G2" s="158"/>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="7"/>
@@ -7666,16 +7695,16 @@
         <v>0</v>
       </c>
       <c r="D4" s="43" t="s">
+        <v>294</v>
+      </c>
+      <c r="E4" s="43" t="s">
+        <v>295</v>
+      </c>
+      <c r="F4" s="43" t="s">
         <v>288</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="G4" s="92" t="s">
         <v>289</v>
-      </c>
-      <c r="F4" s="43" t="s">
-        <v>290</v>
-      </c>
-      <c r="G4" s="92" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7684,21 +7713,21 @@
         <v>1</v>
       </c>
       <c r="C5" s="67" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="D5" s="17">
-        <v>225265</v>
+        <v>361835</v>
       </c>
       <c r="E5" s="70">
-        <v>238368</v>
+        <v>380108</v>
       </c>
       <c r="F5" s="17">
         <f t="shared" ref="F5" si="0">E5-D5</f>
-        <v>13103</v>
+        <v>18273</v>
       </c>
       <c r="G5" s="71">
         <f t="shared" ref="G5" si="1">E5/D5-1</f>
-        <v>5.8167047699376306E-2</v>
+        <v>5.0500918927135263E-2</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="108" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7707,21 +7736,21 @@
         <v>2</v>
       </c>
       <c r="C6" s="67" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="D6" s="109">
-        <v>219264</v>
+        <v>308349</v>
       </c>
       <c r="E6" s="109">
-        <v>230717</v>
+        <v>287012</v>
       </c>
       <c r="F6" s="17">
         <f t="shared" ref="F6:F19" si="2">E6-D6</f>
-        <v>11453</v>
+        <v>-21337</v>
       </c>
       <c r="G6" s="71">
         <f t="shared" ref="G6:G19" si="3">E6/D6-1</f>
-        <v>5.2233836835960279E-2</v>
+        <v>-6.9197565096692393E-2</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="108" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7733,18 +7762,18 @@
         <v>3</v>
       </c>
       <c r="D7" s="109">
-        <v>180805</v>
+        <v>209983</v>
       </c>
       <c r="E7" s="109">
-        <v>160473</v>
+        <v>199577</v>
       </c>
       <c r="F7" s="17">
         <f t="shared" si="2"/>
-        <v>-20332</v>
+        <v>-10406</v>
       </c>
       <c r="G7" s="71">
         <f t="shared" si="3"/>
-        <v>-0.11245264234949259</v>
+        <v>-4.9556392660358273E-2</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="108" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -7756,18 +7785,18 @@
         <v>53</v>
       </c>
       <c r="D8" s="109">
-        <v>80896</v>
+        <v>90398</v>
       </c>
       <c r="E8" s="109">
-        <v>66744</v>
+        <v>79884</v>
       </c>
       <c r="F8" s="17">
         <f t="shared" si="2"/>
-        <v>-14152</v>
+        <v>-10514</v>
       </c>
       <c r="G8" s="71">
         <f t="shared" si="3"/>
-        <v>-0.174940664556962</v>
+        <v>-0.11630788291776362</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="108" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7779,18 +7808,18 @@
         <v>4</v>
       </c>
       <c r="D9" s="109">
-        <v>64818</v>
+        <v>70430</v>
       </c>
       <c r="E9" s="109">
-        <v>59571</v>
+        <v>73774</v>
       </c>
       <c r="F9" s="17">
         <f t="shared" si="2"/>
-        <v>-5247</v>
+        <v>3344</v>
       </c>
       <c r="G9" s="71">
         <f t="shared" si="3"/>
-        <v>-8.0949736184393273E-2</v>
+        <v>4.7479767144682716E-2</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="108" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7799,21 +7828,21 @@
         <v>6</v>
       </c>
       <c r="C10" s="67" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D10" s="109">
-        <v>24192</v>
+        <v>41088</v>
       </c>
       <c r="E10" s="109">
-        <v>30119</v>
+        <v>44943</v>
       </c>
       <c r="F10" s="17">
         <f t="shared" si="2"/>
-        <v>5927</v>
+        <v>3855</v>
       </c>
       <c r="G10" s="71">
         <f t="shared" si="3"/>
-        <v>0.24499834656084651</v>
+        <v>9.3823014018691531E-2</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="108" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -7822,21 +7851,21 @@
         <v>7</v>
       </c>
       <c r="C11" s="67" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D11" s="109">
-        <v>21625</v>
+        <v>32269</v>
       </c>
       <c r="E11" s="109">
-        <v>21583</v>
+        <v>39131</v>
       </c>
       <c r="F11" s="17">
         <f t="shared" si="2"/>
-        <v>-42</v>
+        <v>6862</v>
       </c>
       <c r="G11" s="71">
         <f t="shared" si="3"/>
-        <v>-1.942196531791951E-3</v>
+        <v>0.21264991167994052</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="108" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7848,18 +7877,18 @@
         <v>150</v>
       </c>
       <c r="D12" s="109">
-        <v>13875</v>
+        <v>32880</v>
       </c>
       <c r="E12" s="109">
-        <v>20612</v>
+        <v>33942</v>
       </c>
       <c r="F12" s="17">
         <f t="shared" si="2"/>
-        <v>6737</v>
+        <v>1062</v>
       </c>
       <c r="G12" s="71">
         <f t="shared" si="3"/>
-        <v>0.48554954954954965</v>
+        <v>3.2299270072992714E-2</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
@@ -7868,21 +7897,21 @@
         <v>9</v>
       </c>
       <c r="C13" s="67" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
       <c r="D13" s="17">
-        <v>26372</v>
+        <v>28871</v>
       </c>
       <c r="E13" s="17">
-        <v>18587</v>
+        <v>29316</v>
       </c>
       <c r="F13" s="17">
         <f t="shared" si="2"/>
-        <v>-7785</v>
+        <v>445</v>
       </c>
       <c r="G13" s="71">
         <f t="shared" si="3"/>
-        <v>-0.29519945396632796</v>
+        <v>1.5413390599563481E-2</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7891,21 +7920,21 @@
         <v>10</v>
       </c>
       <c r="C14" s="67" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="D14" s="17">
-        <v>17377</v>
+        <v>22180</v>
       </c>
       <c r="E14" s="17">
-        <v>16904</v>
+        <v>26841</v>
       </c>
       <c r="F14" s="17">
         <f t="shared" si="2"/>
-        <v>-473</v>
+        <v>4661</v>
       </c>
       <c r="G14" s="71">
         <f t="shared" si="3"/>
-        <v>-2.7219888358174571E-2</v>
+        <v>0.21014427412082948</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
@@ -7914,21 +7943,21 @@
         <v>11</v>
       </c>
       <c r="C15" s="67" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D15" s="17">
-        <v>10212</v>
+        <v>23493</v>
       </c>
       <c r="E15" s="17">
-        <v>14051</v>
+        <v>25855</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" si="2"/>
-        <v>3839</v>
+        <v>2362</v>
       </c>
       <c r="G15" s="71">
         <f t="shared" si="3"/>
-        <v>0.37593027810419111</v>
+        <v>0.10054058655769804</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
@@ -7937,21 +7966,21 @@
         <v>12</v>
       </c>
       <c r="C16" s="67" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="D16" s="17">
-        <v>26859</v>
+        <v>19225</v>
       </c>
       <c r="E16" s="17">
-        <v>13757</v>
+        <v>19769</v>
       </c>
       <c r="F16" s="17">
         <f t="shared" si="2"/>
-        <v>-13102</v>
+        <v>544</v>
       </c>
       <c r="G16" s="71">
         <f t="shared" si="3"/>
-        <v>-0.48780669421795297</v>
+        <v>2.8296488946683906E-2</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7960,21 +7989,21 @@
         <v>13</v>
       </c>
       <c r="C17" s="67" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="D17" s="17">
-        <v>10165</v>
+        <v>30433</v>
       </c>
       <c r="E17" s="17">
-        <v>13651</v>
+        <v>15640</v>
       </c>
       <c r="F17" s="17">
         <f t="shared" si="2"/>
-        <v>3486</v>
+        <v>-14793</v>
       </c>
       <c r="G17" s="71">
         <f t="shared" si="3"/>
-        <v>0.34294146581406793</v>
+        <v>-0.48608418493083161</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7983,21 +8012,21 @@
         <v>14</v>
       </c>
       <c r="C18" s="67" t="s">
-        <v>29</v>
+        <v>296</v>
       </c>
       <c r="D18" s="17">
-        <v>6506</v>
+        <v>14666</v>
       </c>
       <c r="E18" s="17">
-        <v>9479</v>
+        <v>14176</v>
       </c>
       <c r="F18" s="17">
         <f t="shared" si="2"/>
-        <v>2973</v>
+        <v>-490</v>
       </c>
       <c r="G18" s="71">
         <f t="shared" si="3"/>
-        <v>0.45696280356593921</v>
+        <v>-3.3410609573162442E-2</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -8006,21 +8035,21 @@
         <v>15</v>
       </c>
       <c r="C19" s="68" t="s">
-        <v>296</v>
+        <v>29</v>
       </c>
       <c r="D19" s="19">
-        <v>7558</v>
+        <v>12398</v>
       </c>
       <c r="E19" s="19">
-        <v>9015</v>
+        <v>13320</v>
       </c>
       <c r="F19" s="19">
         <f t="shared" si="2"/>
-        <v>1457</v>
+        <v>922</v>
       </c>
       <c r="G19" s="72">
         <f t="shared" si="3"/>
-        <v>0.19277586663138391</v>
+        <v>7.4366833360219431E-2</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8040,10 +8069,10 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="154"/>
-      <c r="C24" s="154"/>
-      <c r="D24" s="154"/>
-      <c r="E24" s="154"/>
+      <c r="B24" s="156"/>
+      <c r="C24" s="156"/>
+      <c r="D24" s="156"/>
+      <c r="E24" s="156"/>
       <c r="F24" s="95"/>
     </row>
   </sheetData>
@@ -8075,31 +8104,31 @@
   <sheetData>
     <row r="1" spans="2:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:7" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="155" t="s">
+      <c r="B2" s="157" t="s">
         <v>251</v>
       </c>
-      <c r="C2" s="156"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156"/>
-      <c r="F2" s="156"/>
-      <c r="G2" s="157"/>
+      <c r="C2" s="158"/>
+      <c r="D2" s="158"/>
+      <c r="E2" s="158"/>
+      <c r="F2" s="158"/>
+      <c r="G2" s="159"/>
     </row>
     <row r="3" spans="2:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="96" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C4" s="43" t="s">
+        <v>294</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>295</v>
+      </c>
+      <c r="E4" s="43" t="s">
         <v>288</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="F4" s="92" t="s">
         <v>289</v>
-      </c>
-      <c r="E4" s="43" t="s">
-        <v>290</v>
-      </c>
-      <c r="F4" s="92" t="s">
-        <v>291</v>
       </c>
       <c r="G4" s="98" t="s">
         <v>223</v>
@@ -8110,18 +8139,18 @@
         <v>248</v>
       </c>
       <c r="C5" s="17">
-        <v>1314828</v>
+        <v>1838913</v>
       </c>
       <c r="D5" s="17">
-        <v>1300505</v>
+        <v>1749668</v>
       </c>
       <c r="E5" s="131">
         <f>D5-C5</f>
-        <v>-14323</v>
+        <v>-89245</v>
       </c>
       <c r="F5" s="132">
         <f>D5/C5-1</f>
-        <v>-1.0893440054516645E-2</v>
+        <v>-4.8531387836183604E-2</v>
       </c>
       <c r="G5" s="133">
         <v>1</v>
@@ -8132,22 +8161,22 @@
         <v>249</v>
       </c>
       <c r="C6" s="17">
-        <v>1172336</v>
+        <v>1638188</v>
       </c>
       <c r="D6" s="17">
-        <v>1170362</v>
+        <v>1564142</v>
       </c>
       <c r="E6" s="131">
         <f t="shared" ref="E6:E9" si="0">D6-C6</f>
-        <v>-1974</v>
+        <v>-74046</v>
       </c>
       <c r="F6" s="132">
         <f>D6/C6-1</f>
-        <v>-1.6838176086036993E-3</v>
+        <v>-4.5199940421978391E-2</v>
       </c>
       <c r="G6" s="133">
         <f>D6/D5</f>
-        <v>0.89992887378364561</v>
+        <v>0.89396502650788612</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
@@ -8155,22 +8184,22 @@
         <v>235</v>
       </c>
       <c r="C7" s="17">
-        <v>958947</v>
+        <v>1311416</v>
       </c>
       <c r="D7" s="17">
-        <v>997529</v>
+        <v>1275435</v>
       </c>
       <c r="E7" s="131">
         <f t="shared" si="0"/>
-        <v>38582</v>
+        <v>-35981</v>
       </c>
       <c r="F7" s="132">
         <f>D7/C7-1</f>
-        <v>4.0233714689132949E-2</v>
+        <v>-2.7436755385018996E-2</v>
       </c>
       <c r="G7" s="133">
         <f>D7/D6</f>
-        <v>0.85232517802184282</v>
+        <v>0.81542148986473095</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
@@ -8178,22 +8207,22 @@
         <v>224</v>
       </c>
       <c r="C8" s="17">
-        <v>213389</v>
+        <v>326772</v>
       </c>
       <c r="D8" s="17">
-        <v>172833</v>
+        <v>288707</v>
       </c>
       <c r="E8" s="131">
         <f t="shared" si="0"/>
-        <v>-40556</v>
+        <v>-38065</v>
       </c>
       <c r="F8" s="132">
         <f>D8/C8-1</f>
-        <v>-0.19005665709104036</v>
+        <v>-0.11648794878386148</v>
       </c>
       <c r="G8" s="113">
         <f>D8/D6</f>
-        <v>0.14767482197815718</v>
+        <v>0.18457851013526905</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -8202,23 +8231,23 @@
       </c>
       <c r="C9" s="19">
         <f t="shared" ref="C9" si="1">C5-C6</f>
-        <v>142492</v>
+        <v>200725</v>
       </c>
       <c r="D9" s="19">
         <f>D5-D6</f>
-        <v>130143</v>
+        <v>185526</v>
       </c>
       <c r="E9" s="137">
         <f t="shared" si="0"/>
-        <v>-12349</v>
+        <v>-15199</v>
       </c>
       <c r="F9" s="138">
         <f t="shared" ref="F9" si="2">D9/C9-1</f>
-        <v>-8.6664514499059542E-2</v>
+        <v>-7.572051313986794E-2</v>
       </c>
       <c r="G9" s="120">
         <f>D9/D5</f>
-        <v>0.10007112621635442</v>
+        <v>0.10603497349211394</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
@@ -8243,7 +8272,7 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C15" s="116"/>
-      <c r="D15" s="111"/>
+      <c r="D15" s="152"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C16" s="134"/>
@@ -8313,14 +8342,14 @@
   <sheetData>
     <row r="1" spans="1:7" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:7" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="155" t="s">
+      <c r="B2" s="157" t="s">
         <v>249</v>
       </c>
-      <c r="C2" s="156"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156"/>
-      <c r="F2" s="156"/>
-      <c r="G2" s="157"/>
+      <c r="C2" s="158"/>
+      <c r="D2" s="158"/>
+      <c r="E2" s="158"/>
+      <c r="F2" s="158"/>
+      <c r="G2" s="159"/>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2"/>
@@ -8335,16 +8364,16 @@
         <v>210</v>
       </c>
       <c r="C4" s="43" t="s">
+        <v>294</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>295</v>
+      </c>
+      <c r="E4" s="43" t="s">
         <v>288</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="F4" s="92" t="s">
         <v>289</v>
-      </c>
-      <c r="E4" s="43" t="s">
-        <v>290</v>
-      </c>
-      <c r="F4" s="92" t="s">
-        <v>291</v>
       </c>
       <c r="G4" s="98" t="s">
         <v>223</v>
@@ -8356,20 +8385,20 @@
         <v>219</v>
       </c>
       <c r="C5" s="47">
-        <f>'2026'!C4</f>
-        <v>1172336</v>
+        <f>'2026 II კვარტალი'!C4</f>
+        <v>1638188</v>
       </c>
       <c r="D5" s="47">
-        <f>'2026'!D4</f>
-        <v>1170362</v>
+        <f>'2026 II კვარტალი'!D4</f>
+        <v>1564142</v>
       </c>
       <c r="E5" s="47">
         <f>D5-C5</f>
-        <v>-1974</v>
+        <v>-74046</v>
       </c>
       <c r="F5" s="121">
         <f>D5/C5-1</f>
-        <v>-1.6838176086036993E-3</v>
+        <v>-4.5199940421978391E-2</v>
       </c>
       <c r="G5" s="124">
         <f>D5/D5</f>
@@ -8382,24 +8411,24 @@
         <v>1</v>
       </c>
       <c r="C6" s="25">
-        <f>'2026'!C6</f>
-        <v>933040</v>
+        <f>'2026 II კვარტალი'!C6</f>
+        <v>1310994</v>
       </c>
       <c r="D6" s="25">
-        <f>'2026'!D6</f>
-        <v>946150</v>
+        <f>'2026 II კვარტალი'!D6</f>
+        <v>1330596</v>
       </c>
       <c r="E6" s="25">
         <f>D6-C6</f>
-        <v>13110</v>
+        <v>19602</v>
       </c>
       <c r="F6" s="122">
         <f>D6/C6-1</f>
-        <v>1.4050844551144692E-2</v>
+        <v>1.4952013510359352E-2</v>
       </c>
       <c r="G6" s="125">
         <f>D6/D5</f>
-        <v>0.80842508557181458</v>
+        <v>0.85068746955199714</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8408,24 +8437,24 @@
         <v>55</v>
       </c>
       <c r="C7" s="25">
-        <f>'2026'!C66</f>
-        <v>10920</v>
+        <f>'2026 II კვარტალი'!C66</f>
+        <v>20239</v>
       </c>
       <c r="D7" s="25">
-        <f>'2026'!D66</f>
-        <v>12909</v>
+        <f>'2026 II კვარტალი'!D66</f>
+        <v>20228</v>
       </c>
       <c r="E7" s="25">
         <f t="shared" ref="E7:E10" si="0">D7-C7</f>
-        <v>1989</v>
+        <v>-11</v>
       </c>
       <c r="F7" s="122">
         <f t="shared" ref="F7:F10" si="1">D7/C7-1</f>
-        <v>0.18214285714285716</v>
+        <v>-5.4350511388900902E-4</v>
       </c>
       <c r="G7" s="125">
         <f>D7/D5</f>
-        <v>1.1029920657027483E-2</v>
+        <v>1.2932329673392825E-2</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="24" x14ac:dyDescent="0.2">
@@ -8434,24 +8463,24 @@
         <v>198</v>
       </c>
       <c r="C8" s="25">
-        <f>'2026'!C114</f>
-        <v>90672</v>
+        <f>'2026 II კვარტალი'!C114</f>
+        <v>151759</v>
       </c>
       <c r="D8" s="25">
-        <f>'2026'!D114</f>
-        <v>70833</v>
+        <f>'2026 II კვარტალი'!D114</f>
+        <v>88125</v>
       </c>
       <c r="E8" s="25">
         <f t="shared" si="0"/>
-        <v>-19839</v>
+        <v>-63634</v>
       </c>
       <c r="F8" s="122">
         <f>D8/C8-1</f>
-        <v>-0.21879962943356268</v>
+        <v>-0.41930956318900359</v>
       </c>
       <c r="G8" s="125">
         <f>D8/D5</f>
-        <v>6.0522299937967913E-2</v>
+        <v>5.6340792587885241E-2</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8460,24 +8489,24 @@
         <v>204</v>
       </c>
       <c r="C9" s="25">
-        <f>'2026'!C174</f>
-        <v>4428</v>
+        <f>'2026 II კვარტალი'!C174</f>
+        <v>3760</v>
       </c>
       <c r="D9" s="25">
-        <f>'2026'!D174</f>
-        <v>3625</v>
+        <f>'2026 II კვარტალი'!D174</f>
+        <v>2517</v>
       </c>
       <c r="E9" s="25">
         <f t="shared" si="0"/>
-        <v>-803</v>
+        <v>-1243</v>
       </c>
       <c r="F9" s="122">
         <f t="shared" si="1"/>
-        <v>-0.18134598012646796</v>
+        <v>-0.33058510638297878</v>
       </c>
       <c r="G9" s="125">
         <f>D9/D5</f>
-        <v>3.0973322783890795E-3</v>
+        <v>1.6091889355314287E-3</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -8486,24 +8515,24 @@
         <v>203</v>
       </c>
       <c r="C10" s="26">
-        <f>'2026'!C160</f>
-        <v>26785</v>
+        <f>'2026 II კვარტალი'!C160</f>
+        <v>52891</v>
       </c>
       <c r="D10" s="26">
-        <f>'2026'!D160</f>
-        <v>27779</v>
+        <f>'2026 II კვარტალი'!D160</f>
+        <v>22395</v>
       </c>
       <c r="E10" s="26">
         <f t="shared" si="0"/>
-        <v>994</v>
+        <v>-30496</v>
       </c>
       <c r="F10" s="123">
         <f t="shared" si="1"/>
-        <v>3.7110322941945162E-2</v>
+        <v>-0.57658202718799045</v>
       </c>
       <c r="G10" s="126">
         <f>D10/D5</f>
-        <v>2.3735391272102137E-2</v>
+        <v>1.4317753758929816E-2</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8518,11 +8547,11 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="158"/>
-      <c r="C15" s="158"/>
-      <c r="D15" s="158"/>
-      <c r="E15" s="158"/>
-      <c r="F15" s="158"/>
+      <c r="B15" s="160"/>
+      <c r="C15" s="160"/>
+      <c r="D15" s="160"/>
+      <c r="E15" s="160"/>
+      <c r="F15" s="160"/>
     </row>
     <row r="21" spans="3:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C21" s="3"/>
@@ -8552,13 +8581,13 @@
   <sheetData>
     <row r="1" spans="2:7" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:7" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="155" t="s">
+      <c r="B2" s="157" t="s">
         <v>249</v>
       </c>
-      <c r="C2" s="156"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156"/>
-      <c r="F2" s="157"/>
+      <c r="C2" s="158"/>
+      <c r="D2" s="158"/>
+      <c r="E2" s="158"/>
+      <c r="F2" s="159"/>
     </row>
     <row r="3" spans="2:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2"/>
@@ -8572,16 +8601,16 @@
         <v>287</v>
       </c>
       <c r="C4" s="43" t="s">
+        <v>294</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>295</v>
+      </c>
+      <c r="E4" s="43" t="s">
         <v>288</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="F4" s="92" t="s">
         <v>289</v>
-      </c>
-      <c r="E4" s="43" t="s">
-        <v>290</v>
-      </c>
-      <c r="F4" s="92" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8590,19 +8619,19 @@
       </c>
       <c r="C5" s="47">
         <f>SUM(C6:C33)</f>
-        <v>73886</v>
+        <v>128100</v>
       </c>
       <c r="D5" s="47">
         <f>SUM(D6:D33)</f>
-        <v>96226</v>
+        <v>152975</v>
       </c>
       <c r="E5" s="47">
         <f t="shared" ref="E5" si="0">D5-C5</f>
-        <v>22340</v>
+        <v>24875</v>
       </c>
       <c r="F5" s="124">
-        <f>D5/C5-1</f>
-        <v>0.30235768616517333</v>
+        <f t="shared" ref="F5:F33" si="1">D5/C5-1</f>
+        <v>0.19418423106947702</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8610,18 +8639,18 @@
         <v>60</v>
       </c>
       <c r="C6" s="16">
-        <v>1478</v>
+        <v>2230</v>
       </c>
       <c r="D6" s="16">
-        <v>1537</v>
+        <v>2884</v>
       </c>
       <c r="E6" s="16">
-        <f t="shared" ref="E6:E33" si="1">D6-C6</f>
-        <v>59</v>
+        <f t="shared" ref="E6:E33" si="2">D6-C6</f>
+        <v>654</v>
       </c>
       <c r="F6" s="71">
-        <f t="shared" ref="F5:F33" si="2">D6/C6-1</f>
-        <v>3.9918809201623828E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.29327354260089677</v>
       </c>
       <c r="G6" s="114"/>
     </row>
@@ -8630,18 +8659,18 @@
         <v>44</v>
       </c>
       <c r="C7" s="16">
-        <v>1371</v>
+        <v>2307</v>
       </c>
       <c r="D7" s="16">
-        <v>1632</v>
+        <v>2687</v>
       </c>
       <c r="E7" s="16">
-        <f t="shared" si="1"/>
-        <v>261</v>
+        <f t="shared" si="2"/>
+        <v>380</v>
       </c>
       <c r="F7" s="71">
-        <f t="shared" si="2"/>
-        <v>0.19037199124726478</v>
+        <f t="shared" si="1"/>
+        <v>0.16471608149111394</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8649,18 +8678,18 @@
         <v>6</v>
       </c>
       <c r="C8" s="16">
-        <v>1837</v>
+        <v>2674</v>
       </c>
       <c r="D8" s="16">
-        <v>2136</v>
+        <v>3087</v>
       </c>
       <c r="E8" s="16">
-        <f t="shared" si="1"/>
-        <v>299</v>
+        <f t="shared" si="2"/>
+        <v>413</v>
       </c>
       <c r="F8" s="71">
-        <f t="shared" si="2"/>
-        <v>0.16276537833424065</v>
+        <f t="shared" si="1"/>
+        <v>0.15445026178010468</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8668,18 +8697,18 @@
         <v>29</v>
       </c>
       <c r="C9" s="16">
-        <v>6506</v>
+        <v>12398</v>
       </c>
       <c r="D9" s="16">
-        <v>9479</v>
+        <v>13320</v>
       </c>
       <c r="E9" s="16">
-        <f t="shared" si="1"/>
-        <v>2973</v>
+        <f t="shared" si="2"/>
+        <v>922</v>
       </c>
       <c r="F9" s="71">
-        <f t="shared" si="2"/>
-        <v>0.45696280356593921</v>
+        <f t="shared" si="1"/>
+        <v>7.4366833360219431E-2</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8687,18 +8716,18 @@
         <v>46</v>
       </c>
       <c r="C10" s="16">
-        <v>10212</v>
+        <v>22180</v>
       </c>
       <c r="D10" s="16">
-        <v>14051</v>
+        <v>26841</v>
       </c>
       <c r="E10" s="16">
-        <f t="shared" si="1"/>
-        <v>3839</v>
+        <f t="shared" si="2"/>
+        <v>4661</v>
       </c>
       <c r="F10" s="71">
-        <f t="shared" si="2"/>
-        <v>0.37593027810419111</v>
+        <f t="shared" si="1"/>
+        <v>0.21014427412082948</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8706,18 +8735,18 @@
         <v>23</v>
       </c>
       <c r="C11" s="16">
-        <v>863</v>
+        <v>1077</v>
       </c>
       <c r="D11" s="16">
-        <v>849</v>
+        <v>1253</v>
       </c>
       <c r="E11" s="16">
-        <f t="shared" si="1"/>
-        <v>-14</v>
+        <f t="shared" si="2"/>
+        <v>176</v>
       </c>
       <c r="F11" s="71">
-        <f t="shared" si="2"/>
-        <v>-1.6222479721900385E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.16341689879294341</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8725,18 +8754,18 @@
         <v>42</v>
       </c>
       <c r="C12" s="16">
-        <v>2988</v>
+        <v>4966</v>
       </c>
       <c r="D12" s="16">
-        <v>4315</v>
+        <v>6737</v>
       </c>
       <c r="E12" s="16">
-        <f t="shared" si="1"/>
-        <v>1327</v>
+        <f t="shared" si="2"/>
+        <v>1771</v>
       </c>
       <c r="F12" s="71">
-        <f t="shared" si="2"/>
-        <v>0.44410977242302541</v>
+        <f t="shared" si="1"/>
+        <v>0.35662505034232783</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8744,18 +8773,18 @@
         <v>8</v>
       </c>
       <c r="C13" s="16">
-        <v>1332</v>
+        <v>1708</v>
       </c>
       <c r="D13" s="16">
-        <v>1138</v>
+        <v>1698</v>
       </c>
       <c r="E13" s="16">
-        <f t="shared" si="1"/>
-        <v>-194</v>
+        <f t="shared" si="2"/>
+        <v>-10</v>
       </c>
       <c r="F13" s="71">
-        <f t="shared" si="2"/>
-        <v>-0.14564564564564564</v>
+        <f t="shared" si="1"/>
+        <v>-5.8548009367681564E-3</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8763,18 +8792,18 @@
         <v>26</v>
       </c>
       <c r="C14" s="16">
-        <v>1015</v>
+        <v>1359</v>
       </c>
       <c r="D14" s="16">
-        <v>1113</v>
+        <v>1434</v>
       </c>
       <c r="E14" s="16">
-        <f t="shared" si="1"/>
-        <v>98</v>
+        <f t="shared" si="2"/>
+        <v>75</v>
       </c>
       <c r="F14" s="71">
-        <f t="shared" si="2"/>
-        <v>9.6551724137931005E-2</v>
+        <f t="shared" si="1"/>
+        <v>5.5187637969094983E-2</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8782,37 +8811,37 @@
         <v>36</v>
       </c>
       <c r="C15" s="16">
-        <v>4170</v>
+        <v>6815</v>
       </c>
       <c r="D15" s="16">
-        <v>7117</v>
+        <v>8459</v>
       </c>
       <c r="E15" s="16">
-        <f t="shared" si="1"/>
-        <v>2947</v>
+        <f t="shared" si="2"/>
+        <v>1644</v>
       </c>
       <c r="F15" s="71">
+        <f t="shared" si="1"/>
+        <v>0.24123257520176078</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="127" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="139">
+        <v>1536</v>
+      </c>
+      <c r="D16" s="139">
+        <v>2009</v>
+      </c>
+      <c r="E16" s="139">
         <f t="shared" si="2"/>
-        <v>0.7067146282973622</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="16">
-        <v>1363</v>
-      </c>
-      <c r="D16" s="16">
-        <v>1750</v>
-      </c>
-      <c r="E16" s="16">
-        <f t="shared" si="1"/>
-        <v>387</v>
-      </c>
-      <c r="F16" s="71">
-        <f t="shared" si="2"/>
-        <v>0.28393250183418939</v>
+        <v>473</v>
+      </c>
+      <c r="F16" s="113">
+        <f t="shared" si="1"/>
+        <v>0.30794270833333326</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8820,37 +8849,37 @@
         <v>12</v>
       </c>
       <c r="C17" s="16">
-        <v>3375</v>
+        <v>4671</v>
       </c>
       <c r="D17" s="16">
-        <v>2508</v>
+        <v>5337</v>
       </c>
       <c r="E17" s="16">
-        <f t="shared" si="1"/>
-        <v>-867</v>
+        <f t="shared" si="2"/>
+        <v>666</v>
       </c>
       <c r="F17" s="71">
-        <f t="shared" si="2"/>
-        <v>-0.25688888888888894</v>
+        <f t="shared" si="1"/>
+        <v>0.1425818882466281</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="127" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C18" s="16">
-        <v>3441</v>
+        <v>4679</v>
       </c>
       <c r="D18" s="16">
-        <v>4470</v>
+        <v>6324</v>
       </c>
       <c r="E18" s="16">
-        <f t="shared" si="1"/>
-        <v>1029</v>
+        <f t="shared" si="2"/>
+        <v>1645</v>
       </c>
       <c r="F18" s="71">
-        <f t="shared" si="2"/>
-        <v>0.29904097646033123</v>
+        <f t="shared" si="1"/>
+        <v>0.35157084847189579</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8858,37 +8887,37 @@
         <v>48</v>
       </c>
       <c r="C19" s="16">
-        <v>75</v>
+        <v>169</v>
       </c>
       <c r="D19" s="16">
-        <v>102</v>
+        <v>199</v>
       </c>
       <c r="E19" s="16">
-        <f t="shared" si="1"/>
-        <v>27</v>
+        <f t="shared" si="2"/>
+        <v>30</v>
       </c>
       <c r="F19" s="71">
-        <f t="shared" si="2"/>
-        <v>0.3600000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <f t="shared" si="1"/>
+        <v>0.1775147928994083</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" s="107" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="31" t="s">
         <v>37</v>
       </c>
       <c r="C20" s="16">
-        <v>94</v>
+        <v>164</v>
       </c>
       <c r="D20" s="16">
-        <v>143</v>
+        <v>233</v>
       </c>
       <c r="E20" s="16">
-        <f t="shared" si="1"/>
-        <v>49</v>
+        <f t="shared" si="2"/>
+        <v>69</v>
       </c>
       <c r="F20" s="71">
-        <f t="shared" si="2"/>
-        <v>0.52127659574468077</v>
+        <f t="shared" si="1"/>
+        <v>0.4207317073170731</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8897,18 +8926,18 @@
         <v>49</v>
       </c>
       <c r="C21" s="16">
-        <v>2736</v>
+        <v>4885</v>
       </c>
       <c r="D21" s="16">
-        <v>3441</v>
+        <v>6621</v>
       </c>
       <c r="E21" s="16">
-        <f t="shared" si="1"/>
-        <v>705</v>
+        <f t="shared" si="2"/>
+        <v>1736</v>
       </c>
       <c r="F21" s="71">
-        <f t="shared" si="2"/>
-        <v>0.25767543859649122</v>
+        <f t="shared" si="1"/>
+        <v>0.3553735926305015</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="107" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8917,18 +8946,18 @@
         <v>14</v>
       </c>
       <c r="C22" s="139">
-        <v>10165</v>
+        <v>23493</v>
       </c>
       <c r="D22" s="139">
-        <v>13651</v>
+        <v>25855</v>
       </c>
       <c r="E22" s="139">
-        <f t="shared" si="1"/>
-        <v>3486</v>
+        <f t="shared" si="2"/>
+        <v>2362</v>
       </c>
       <c r="F22" s="113">
-        <f t="shared" si="2"/>
-        <v>0.34294146581406793</v>
+        <f t="shared" si="1"/>
+        <v>0.10054058655769804</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8936,18 +8965,18 @@
         <v>39</v>
       </c>
       <c r="C23" s="16">
-        <v>892</v>
+        <v>1532</v>
       </c>
       <c r="D23" s="16">
-        <v>1114</v>
+        <v>1933</v>
       </c>
       <c r="E23" s="16">
-        <f t="shared" si="1"/>
-        <v>222</v>
+        <f t="shared" si="2"/>
+        <v>401</v>
       </c>
       <c r="F23" s="71">
-        <f t="shared" si="2"/>
-        <v>0.24887892376681608</v>
+        <f t="shared" si="1"/>
+        <v>0.26174934725848553</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8955,18 +8984,18 @@
         <v>15</v>
       </c>
       <c r="C24" s="16">
-        <v>1473</v>
+        <v>2387</v>
       </c>
       <c r="D24" s="16">
-        <v>1922</v>
+        <v>3155</v>
       </c>
       <c r="E24" s="16">
-        <f t="shared" si="1"/>
-        <v>449</v>
+        <f t="shared" si="2"/>
+        <v>768</v>
       </c>
       <c r="F24" s="71">
-        <f t="shared" si="2"/>
-        <v>0.30482009504412755</v>
+        <f t="shared" si="1"/>
+        <v>0.32174277335567658</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8974,18 +9003,18 @@
         <v>34</v>
       </c>
       <c r="C25" s="16">
-        <v>5825</v>
+        <v>7837</v>
       </c>
       <c r="D25" s="16">
-        <v>7089</v>
+        <v>7925</v>
       </c>
       <c r="E25" s="16">
-        <f t="shared" si="1"/>
-        <v>1264</v>
+        <f t="shared" si="2"/>
+        <v>88</v>
       </c>
       <c r="F25" s="71">
-        <f t="shared" si="2"/>
-        <v>0.21699570815450642</v>
+        <f t="shared" si="1"/>
+        <v>1.1228786525456114E-2</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8993,18 +9022,18 @@
         <v>45</v>
       </c>
       <c r="C26" s="16">
-        <v>5008</v>
+        <v>7877</v>
       </c>
       <c r="D26" s="16">
-        <v>6243</v>
+        <v>10082</v>
       </c>
       <c r="E26" s="16">
-        <f t="shared" si="1"/>
-        <v>1235</v>
+        <f t="shared" si="2"/>
+        <v>2205</v>
       </c>
       <c r="F26" s="71">
-        <f>D26/C26-1</f>
-        <v>0.2466054313099042</v>
+        <f t="shared" si="1"/>
+        <v>0.27992890694426809</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9012,18 +9041,18 @@
         <v>17</v>
       </c>
       <c r="C27" s="16">
-        <v>1240</v>
+        <v>1602</v>
       </c>
       <c r="D27" s="16">
-        <v>2326</v>
+        <v>2422</v>
       </c>
       <c r="E27" s="16">
-        <f t="shared" si="1"/>
-        <v>1086</v>
+        <f t="shared" si="2"/>
+        <v>820</v>
       </c>
       <c r="F27" s="71">
-        <f t="shared" si="2"/>
-        <v>0.87580645161290316</v>
+        <f t="shared" si="1"/>
+        <v>0.51186017478152301</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9031,18 +9060,18 @@
         <v>41</v>
       </c>
       <c r="C28" s="16">
-        <v>415</v>
+        <v>682</v>
       </c>
       <c r="D28" s="16">
-        <v>522</v>
+        <v>962</v>
       </c>
       <c r="E28" s="16">
-        <f t="shared" si="1"/>
-        <v>107</v>
+        <f t="shared" si="2"/>
+        <v>280</v>
       </c>
       <c r="F28" s="71">
-        <f t="shared" si="2"/>
-        <v>0.25783132530120478</v>
+        <f t="shared" si="1"/>
+        <v>0.41055718475073322</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9050,18 +9079,18 @@
         <v>9</v>
       </c>
       <c r="C29" s="16">
-        <v>1204</v>
+        <v>2336</v>
       </c>
       <c r="D29" s="16">
-        <v>1545</v>
+        <v>2950</v>
       </c>
       <c r="E29" s="16">
-        <f t="shared" si="1"/>
-        <v>341</v>
+        <f t="shared" si="2"/>
+        <v>614</v>
       </c>
       <c r="F29" s="71">
-        <f t="shared" si="2"/>
-        <v>0.28322259136212624</v>
+        <f t="shared" si="1"/>
+        <v>0.26284246575342474</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9069,18 +9098,18 @@
         <v>24</v>
       </c>
       <c r="C30" s="16">
-        <v>767</v>
+        <v>888</v>
       </c>
       <c r="D30" s="16">
-        <v>974</v>
+        <v>1335</v>
       </c>
       <c r="E30" s="16">
-        <f t="shared" si="1"/>
-        <v>207</v>
+        <f t="shared" si="2"/>
+        <v>447</v>
       </c>
       <c r="F30" s="71">
-        <f t="shared" si="2"/>
-        <v>0.26988265971316827</v>
+        <f t="shared" si="1"/>
+        <v>0.50337837837837829</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9088,18 +9117,18 @@
         <v>28</v>
       </c>
       <c r="C31" s="16">
-        <v>1485</v>
+        <v>1399</v>
       </c>
       <c r="D31" s="16">
-        <v>1698</v>
+        <v>1859</v>
       </c>
       <c r="E31" s="16">
-        <f t="shared" si="1"/>
-        <v>213</v>
+        <f t="shared" si="2"/>
+        <v>460</v>
       </c>
       <c r="F31" s="71">
-        <f t="shared" si="2"/>
-        <v>0.14343434343434347</v>
+        <f t="shared" si="1"/>
+        <v>0.32880629020729102</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9107,18 +9136,18 @@
         <v>7</v>
       </c>
       <c r="C32" s="16">
-        <v>2259</v>
+        <v>3746</v>
       </c>
       <c r="D32" s="16">
-        <v>2868</v>
+        <v>4637</v>
       </c>
       <c r="E32" s="16">
-        <f t="shared" si="1"/>
-        <v>609</v>
+        <f t="shared" si="2"/>
+        <v>891</v>
       </c>
       <c r="F32" s="71">
-        <f t="shared" si="2"/>
-        <v>0.26958831341301459</v>
+        <f t="shared" si="1"/>
+        <v>0.23785371062466631</v>
       </c>
     </row>
     <row r="33" spans="2:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -9126,18 +9155,18 @@
         <v>33</v>
       </c>
       <c r="C33" s="18">
-        <v>297</v>
+        <v>503</v>
       </c>
       <c r="D33" s="18">
-        <v>493</v>
+        <v>737</v>
       </c>
       <c r="E33" s="18">
-        <f t="shared" si="1"/>
-        <v>196</v>
+        <f t="shared" si="2"/>
+        <v>234</v>
       </c>
       <c r="F33" s="72">
-        <f t="shared" si="2"/>
-        <v>0.65993265993266004</v>
+        <f t="shared" si="1"/>
+        <v>0.46520874751491048</v>
       </c>
     </row>
     <row r="37" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9172,14 +9201,14 @@
     <row r="1" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:7" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="24"/>
-      <c r="B2" s="159" t="s">
+      <c r="B2" s="161" t="s">
         <v>249</v>
       </c>
-      <c r="C2" s="160"/>
-      <c r="D2" s="160"/>
-      <c r="E2" s="160"/>
-      <c r="F2" s="160"/>
-      <c r="G2" s="161"/>
+      <c r="C2" s="162"/>
+      <c r="D2" s="162"/>
+      <c r="E2" s="162"/>
+      <c r="F2" s="162"/>
+      <c r="G2" s="163"/>
     </row>
     <row r="3" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9187,16 +9216,16 @@
         <v>214</v>
       </c>
       <c r="C4" s="43" t="s">
+        <v>294</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>295</v>
+      </c>
+      <c r="E4" s="43" t="s">
         <v>288</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="F4" s="92" t="s">
         <v>289</v>
-      </c>
-      <c r="E4" s="43" t="s">
-        <v>290</v>
-      </c>
-      <c r="F4" s="92" t="s">
-        <v>291</v>
       </c>
       <c r="G4" s="98" t="s">
         <v>222</v>
@@ -9207,22 +9236,22 @@
         <v>216</v>
       </c>
       <c r="C5" s="16">
-        <v>659765</v>
+        <v>931760</v>
       </c>
       <c r="D5" s="16">
-        <v>621705</v>
+        <v>895776</v>
       </c>
       <c r="E5" s="103">
         <f>D5-C5</f>
-        <v>-38060</v>
+        <v>-35984</v>
       </c>
       <c r="F5" s="29">
         <f>D5/C5-1</f>
-        <v>-5.7687206808484826E-2</v>
+        <v>-3.8619386966600833E-2</v>
       </c>
       <c r="G5" s="73">
-        <f>D5/'2026'!D4</f>
-        <v>0.53120743838231244</v>
+        <f>D5/'2026 II კვარტალი'!D4</f>
+        <v>0.57269480648176441</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -9230,22 +9259,22 @@
         <v>215</v>
       </c>
       <c r="C6" s="16">
-        <v>503009</v>
+        <v>695791</v>
       </c>
       <c r="D6" s="16">
-        <v>539159</v>
+        <v>652260</v>
       </c>
       <c r="E6" s="103">
         <f t="shared" ref="E6:E8" si="0">D6-C6</f>
-        <v>36150</v>
+        <v>-43531</v>
       </c>
       <c r="F6" s="29">
         <f t="shared" ref="F6:F7" si="1">D6/C6-1</f>
-        <v>7.1867501376714937E-2</v>
+        <v>-6.256332720601443E-2</v>
       </c>
       <c r="G6" s="73">
-        <f>D6/'2026'!D4</f>
-        <v>0.46067712383006282</v>
+        <f>D6/'2026 II კვარტალი'!D4</f>
+        <v>0.41700817444963439</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -9253,22 +9282,22 @@
         <v>286</v>
       </c>
       <c r="C7" s="16">
-        <v>7175</v>
+        <v>7260</v>
       </c>
       <c r="D7" s="16">
-        <v>7086</v>
+        <v>8677</v>
       </c>
       <c r="E7" s="103">
         <f t="shared" si="0"/>
-        <v>-89</v>
+        <v>1417</v>
       </c>
       <c r="F7" s="29">
         <f t="shared" si="1"/>
-        <v>-1.2404181184669016E-2</v>
+        <v>0.19517906336088164</v>
       </c>
       <c r="G7" s="73">
-        <f>D7/'2026'!D4</f>
-        <v>6.0545369723213841E-3</v>
+        <f>D7/'2026 II კვარტალი'!D4</f>
+        <v>5.5474502954335351E-3</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -9276,30 +9305,30 @@
         <v>217</v>
       </c>
       <c r="C8" s="18">
-        <v>2387</v>
+        <v>3377</v>
       </c>
       <c r="D8" s="18">
-        <v>2412</v>
+        <v>7429</v>
       </c>
       <c r="E8" s="104">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>4052</v>
       </c>
       <c r="F8" s="30">
         <f>D8/C8-1</f>
-        <v>1.047339757017185E-2</v>
+        <v>1.1998815516730827</v>
       </c>
       <c r="G8" s="74">
-        <f>D8/'2026'!D4</f>
-        <v>2.0609008153032993E-3</v>
+        <f>D8/'2026 II კვარტალი'!D4</f>
+        <v>4.7495687731676532E-3</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="162" t="s">
+      <c r="B12" s="164" t="s">
         <v>209</v>
       </c>
-      <c r="C12" s="162"/>
-      <c r="D12" s="162"/>
+      <c r="C12" s="164"/>
+      <c r="D12" s="164"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C15" s="140"/>
@@ -9336,7 +9365,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="B1:G33"/>
+  <dimension ref="B1:J33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" customWidth="1"/>
@@ -9344,335 +9373,343 @@
     <col min="3" max="7" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:7" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="159" t="s">
+    <row r="1" spans="2:10" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:10" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="161" t="s">
         <v>249</v>
       </c>
-      <c r="C2" s="160"/>
-      <c r="D2" s="160"/>
-      <c r="E2" s="160"/>
-      <c r="F2" s="160"/>
-      <c r="G2" s="161"/>
-    </row>
-    <row r="3" spans="2:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C2" s="162"/>
+      <c r="D2" s="162"/>
+      <c r="E2" s="162"/>
+      <c r="F2" s="162"/>
+      <c r="G2" s="163"/>
+    </row>
+    <row r="3" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="94" t="s">
         <v>218</v>
       </c>
       <c r="C4" s="43" t="s">
+        <v>294</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>295</v>
+      </c>
+      <c r="E4" s="43" t="s">
         <v>288</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="F4" s="92" t="s">
         <v>289</v>
-      </c>
-      <c r="E4" s="43" t="s">
-        <v>290</v>
-      </c>
-      <c r="F4" s="92" t="s">
-        <v>291</v>
       </c>
       <c r="G4" s="44" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" s="31" t="s">
         <v>265</v>
       </c>
       <c r="C5" s="16">
-        <v>347977</v>
+        <v>455865</v>
       </c>
       <c r="D5" s="16">
-        <v>393560</v>
+        <v>419177</v>
       </c>
       <c r="E5" s="103">
         <f>D5-C5</f>
-        <v>45583</v>
+        <v>-36688</v>
       </c>
       <c r="F5" s="29">
         <f>D5/C5-1</f>
-        <v>0.13099428985249029</v>
+        <v>-8.0479966656795354E-2</v>
       </c>
       <c r="G5" s="27">
-        <f>D5/'2026'!D$4</f>
-        <v>0.33627202523663619</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+        <f>D5/'2026 II კვარტალი'!D$4</f>
+        <v>0.26799165293176708</v>
+      </c>
+      <c r="I5" s="153"/>
+      <c r="J5" s="153"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" s="31" t="s">
         <v>264</v>
       </c>
       <c r="C6" s="15">
-        <v>197239</v>
+        <v>292310</v>
       </c>
       <c r="D6" s="16">
-        <v>191832</v>
+        <v>273601</v>
       </c>
       <c r="E6" s="103">
         <f t="shared" ref="E6:E25" si="0">D6-C6</f>
-        <v>-5407</v>
+        <v>-18709</v>
       </c>
       <c r="F6" s="29">
         <f t="shared" ref="F6:F23" si="1">D6/C6-1</f>
-        <v>-2.7413442574744318E-2</v>
+        <v>-6.400396838972322E-2</v>
       </c>
       <c r="G6" s="27">
-        <f>D6/'2026'!D$4</f>
-        <v>0.16390826086287832</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
+        <f>D6/'2026 II კვარტალი'!D$4</f>
+        <v>0.17492081920950911</v>
+      </c>
+      <c r="I6" s="153"/>
+      <c r="J6" s="153"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B7" s="31" t="s">
         <v>266</v>
       </c>
       <c r="C7" s="15">
-        <v>177522</v>
+        <v>271781</v>
       </c>
       <c r="D7" s="16">
-        <v>152550</v>
+        <v>239589</v>
       </c>
       <c r="E7" s="103">
         <f t="shared" si="0"/>
-        <v>-24972</v>
+        <v>-32192</v>
       </c>
       <c r="F7" s="29">
         <f t="shared" si="1"/>
-        <v>-0.14066988880251463</v>
+        <v>-0.1184483094844746</v>
       </c>
       <c r="G7" s="27">
-        <f>D7/'2026'!D$4</f>
-        <v>0.13034428663951836</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
+        <f>D7/'2026 II კვარტალი'!D$4</f>
+        <v>0.15317599041519248</v>
+      </c>
+      <c r="I7" s="153"/>
+      <c r="J7" s="153"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" s="31" t="s">
         <v>267</v>
       </c>
       <c r="C8" s="15">
-        <v>142625</v>
+        <v>206666</v>
       </c>
       <c r="D8" s="16">
-        <v>136460</v>
+        <v>211424</v>
       </c>
       <c r="E8" s="103">
         <f t="shared" si="0"/>
-        <v>-6165</v>
+        <v>4758</v>
       </c>
       <c r="F8" s="29">
         <f t="shared" si="1"/>
-        <v>-4.3225241016652038E-2</v>
+        <v>2.3022654911790008E-2</v>
       </c>
       <c r="G8" s="27">
-        <f>D8/'2026'!D$4</f>
-        <v>0.1165964035059238</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
+        <f>D8/'2026 II კვარტალი'!D$4</f>
+        <v>0.13516931327206866</v>
+      </c>
+      <c r="I8" s="153"/>
+      <c r="J8" s="153"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B9" s="31" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C9" s="15">
-        <v>89371</v>
+        <v>122050</v>
       </c>
       <c r="D9" s="16">
-        <v>97019</v>
+        <v>118336</v>
       </c>
       <c r="E9" s="103">
         <f t="shared" si="0"/>
-        <v>7648</v>
+        <v>-3714</v>
       </c>
       <c r="F9" s="29">
         <f t="shared" si="1"/>
-        <v>8.557585794049527E-2</v>
+        <v>-3.0430151577222397E-2</v>
       </c>
       <c r="G9" s="27">
-        <f>D9/'2026'!D$4</f>
-        <v>8.2896573880560029E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
+        <f>D9/'2026 II კვარტალი'!D$4</f>
+        <v>7.5655535111262273E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B10" s="31" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C10" s="15">
-        <v>65661</v>
+        <v>117876</v>
       </c>
       <c r="D10" s="16">
-        <v>48580</v>
+        <v>114747</v>
       </c>
       <c r="E10" s="103">
         <f t="shared" si="0"/>
-        <v>-17081</v>
+        <v>-3129</v>
       </c>
       <c r="F10" s="29">
         <f t="shared" si="1"/>
-        <v>-0.2601391998294269</v>
+        <v>-2.6544843734093493E-2</v>
       </c>
       <c r="G10" s="27">
-        <f>D10/'2026'!D$4</f>
-        <v>4.1508524712866618E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
+        <f>D10/'2026 II კვარტალი'!D$4</f>
+        <v>7.336098640660503E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B11" s="31" t="s">
         <v>272</v>
       </c>
       <c r="C11" s="15">
-        <v>47761</v>
+        <v>46953</v>
       </c>
       <c r="D11" s="16">
-        <v>46585</v>
+        <v>51363</v>
       </c>
       <c r="E11" s="103">
         <f t="shared" si="0"/>
-        <v>-1176</v>
+        <v>4410</v>
       </c>
       <c r="F11" s="29">
         <f t="shared" si="1"/>
-        <v>-2.4622600029312602E-2</v>
+        <v>9.3923710944987526E-2</v>
       </c>
       <c r="G11" s="27">
-        <f>D11/'2026'!D$4</f>
-        <v>3.9803923914139387E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
+        <f>D11/'2026 II კვარტალი'!D$4</f>
+        <v>3.2837811400755174E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B12" s="31" t="s">
         <v>270</v>
       </c>
       <c r="C12" s="15">
-        <v>33314</v>
+        <v>33878</v>
       </c>
       <c r="D12" s="16">
-        <v>32936</v>
+        <v>39404</v>
       </c>
       <c r="E12" s="103">
         <f t="shared" si="0"/>
-        <v>-378</v>
+        <v>5526</v>
       </c>
       <c r="F12" s="29">
         <f t="shared" si="1"/>
-        <v>-1.1346581016989821E-2</v>
+        <v>0.16311470570871944</v>
       </c>
       <c r="G12" s="27">
-        <f>D12/'2026'!D$4</f>
-        <v>2.8141720254075235E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
+        <f>D12/'2026 II კვარტალი'!D$4</f>
+        <v>2.5192086140516653E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B13" s="31" t="s">
         <v>271</v>
       </c>
       <c r="C13" s="15">
-        <v>24590</v>
+        <v>26612</v>
       </c>
       <c r="D13" s="16">
-        <v>19928</v>
+        <v>26581</v>
       </c>
       <c r="E13" s="103">
         <f t="shared" si="0"/>
-        <v>-4662</v>
+        <v>-31</v>
       </c>
       <c r="F13" s="29">
         <f t="shared" si="1"/>
-        <v>-0.18958926392842623</v>
+        <v>-1.164888020441901E-3</v>
       </c>
       <c r="G13" s="27">
-        <f>D13/'2026'!D$4</f>
-        <v>1.7027210384479331E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
+        <f>D13/'2026 II კვარტალი'!D$4</f>
+        <v>1.6993981364863294E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B14" s="31" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C14" s="15">
-        <v>13364</v>
+        <v>21030</v>
       </c>
       <c r="D14" s="16">
-        <v>16768</v>
+        <v>20133</v>
       </c>
       <c r="E14" s="103">
         <f t="shared" si="0"/>
-        <v>3404</v>
+        <v>-897</v>
       </c>
       <c r="F14" s="29">
         <f t="shared" si="1"/>
-        <v>0.25471415743789283</v>
+        <v>-4.2653352353780316E-2</v>
       </c>
       <c r="G14" s="27">
-        <f>D14/'2026'!D$4</f>
-        <v>1.4327191074214644E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
+        <f>D14/'2026 II კვარტალი'!D$4</f>
+        <v>1.2871593499822906E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B15" s="31" t="s">
         <v>274</v>
       </c>
       <c r="C15" s="15">
-        <v>12199</v>
+        <v>16455</v>
       </c>
       <c r="D15" s="16">
-        <v>12572</v>
+        <v>17032</v>
       </c>
       <c r="E15" s="103">
         <f t="shared" si="0"/>
-        <v>373</v>
+        <v>577</v>
       </c>
       <c r="F15" s="29">
         <f t="shared" si="1"/>
-        <v>3.0576276743995434E-2</v>
+        <v>3.5065329687025137E-2</v>
       </c>
       <c r="G15" s="27">
-        <f>D15/'2026'!D$4</f>
-        <v>1.0741975559698623E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
+        <f>D15/'2026 II კვარტალი'!D$4</f>
+        <v>1.0889036928872187E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B16" s="31" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C16" s="15">
-        <v>11135</v>
+        <v>16065</v>
       </c>
       <c r="D16" s="16">
-        <v>12071</v>
+        <v>16642</v>
       </c>
       <c r="E16" s="103">
         <f t="shared" si="0"/>
-        <v>936</v>
+        <v>577</v>
       </c>
       <c r="F16" s="29">
         <f t="shared" si="1"/>
-        <v>8.4059272563987486E-2</v>
+        <v>3.5916588857765275E-2</v>
       </c>
       <c r="G16" s="27">
-        <f>D16/'2026'!D$4</f>
-        <v>1.0313902877912987E-2</v>
+        <f>D16/'2026 II კვარტალი'!D$4</f>
+        <v>1.0639698953164099E-2</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="31" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C17" s="15">
-        <v>3846</v>
+        <v>296</v>
       </c>
       <c r="D17" s="16">
-        <v>3464</v>
+        <v>4593</v>
       </c>
       <c r="E17" s="103">
         <f t="shared" si="0"/>
-        <v>-382</v>
+        <v>4297</v>
       </c>
       <c r="F17" s="29">
         <f t="shared" si="1"/>
-        <v>-9.9323972958918372E-2</v>
+        <v>14.516891891891891</v>
       </c>
       <c r="G17" s="27">
-        <f>D17/'2026'!D$4</f>
-        <v>2.959768003404075E-3</v>
+        <f>D17/'2026 II კვარტალი'!D$4</f>
+        <v>2.9364341600698657E-3</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
@@ -9680,91 +9717,91 @@
         <v>278</v>
       </c>
       <c r="C18" s="15">
-        <v>2630</v>
+        <v>3189</v>
       </c>
       <c r="D18" s="16">
-        <v>3053</v>
+        <v>3950</v>
       </c>
       <c r="E18" s="103">
         <f t="shared" si="0"/>
-        <v>423</v>
+        <v>761</v>
       </c>
       <c r="F18" s="29">
         <f t="shared" si="1"/>
-        <v>0.16083650190114063</v>
+        <v>0.23863280025086242</v>
       </c>
       <c r="G18" s="27">
-        <f>D18/'2026'!D$4</f>
-        <v>2.6085946057715476E-3</v>
+        <f>D18/'2026 II კვარტალი'!D$4</f>
+        <v>2.5253461642229416E-3</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B19" s="31" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C19" s="15">
-        <v>1887</v>
+        <v>3397</v>
       </c>
       <c r="D19" s="16">
-        <v>1878</v>
+        <v>3899</v>
       </c>
       <c r="E19" s="103">
         <f t="shared" si="0"/>
-        <v>-9</v>
+        <v>502</v>
       </c>
       <c r="F19" s="29">
         <f t="shared" si="1"/>
-        <v>-4.7694753577106619E-3</v>
+        <v>0.14777745069178683</v>
       </c>
       <c r="G19" s="27">
-        <f>D19/'2026'!D$4</f>
-        <v>1.6046317293281907E-3</v>
+        <f>D19/'2026 II კვარტალი'!D$4</f>
+        <v>2.4927404289380377E-3</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="31" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C20" s="15">
-        <v>699</v>
+        <v>2842</v>
       </c>
       <c r="D20" s="16">
-        <v>569</v>
+        <v>2629</v>
       </c>
       <c r="E20" s="103">
         <f t="shared" si="0"/>
-        <v>-130</v>
+        <v>-213</v>
       </c>
       <c r="F20" s="29">
         <f t="shared" si="1"/>
-        <v>-0.18597997138769673</v>
+        <v>-7.4947220267417292E-2</v>
       </c>
       <c r="G20" s="27">
-        <f>D20/'2026'!D$4</f>
-        <v>4.8617436314576175E-4</v>
+        <f>D20/'2026 II კვარტალი'!D$4</f>
+        <v>1.6807936875296488E-3</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B21" s="31" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C21" s="15">
-        <v>267</v>
+        <v>674</v>
       </c>
       <c r="D21" s="16">
-        <v>370</v>
+        <v>828</v>
       </c>
       <c r="E21" s="103">
         <f t="shared" si="0"/>
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="F21" s="29">
         <f t="shared" si="1"/>
-        <v>0.38576779026217234</v>
+        <v>0.228486646884273</v>
       </c>
       <c r="G21" s="27">
-        <f>D21/'2026'!D$4</f>
-        <v>3.1614150151833362E-4</v>
+        <f>D21/'2026 II კვარტალი'!D$4</f>
+        <v>5.2936370227255579E-4</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
@@ -9772,22 +9809,22 @@
         <v>281</v>
       </c>
       <c r="C22" s="15">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="D22" s="16">
-        <v>164</v>
+        <v>207</v>
       </c>
       <c r="E22" s="103">
         <f t="shared" si="0"/>
-        <v>-69</v>
+        <v>-32</v>
       </c>
       <c r="F22" s="29">
         <f t="shared" si="1"/>
-        <v>-0.29613733905579398</v>
+        <v>-0.13389121338912136</v>
       </c>
       <c r="G22" s="27">
-        <f>D22/'2026'!D$4</f>
-        <v>1.4012758445677492E-4</v>
+        <f>D22/'2026 II კვარტალი'!D$4</f>
+        <v>1.3234092556813895E-4</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
@@ -9795,22 +9832,22 @@
         <v>282</v>
       </c>
       <c r="C23" s="15">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D23" s="16">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E23" s="103">
         <f t="shared" si="0"/>
-        <v>-13</v>
+        <v>-3</v>
       </c>
       <c r="F23" s="29">
         <f t="shared" si="1"/>
-        <v>-0.8125</v>
+        <v>-0.30000000000000004</v>
       </c>
       <c r="G23" s="27">
-        <f>D23/'2026'!D$4</f>
-        <v>2.563309471770273E-6</v>
+        <f>D23/'2026 II კვარტალი'!D$4</f>
+        <v>4.4752969998887569E-6</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.2">
@@ -9829,7 +9866,7 @@
       </c>
       <c r="F24" s="29"/>
       <c r="G24" s="27">
-        <f>D24/'2026'!D$4</f>
+        <f>D24/'2026 II კვარტალი'!D$4</f>
         <v>0</v>
       </c>
     </row>
@@ -9849,7 +9886,7 @@
       </c>
       <c r="F25" s="30"/>
       <c r="G25" s="28">
-        <f>D25/'2026'!D$4</f>
+        <f>D25/'2026 II კვარტალი'!D$4</f>
         <v>0</v>
       </c>
     </row>
@@ -9867,17 +9904,20 @@
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B30" s="163"/>
-      <c r="C30" s="163"/>
-      <c r="D30" s="163"/>
-      <c r="E30" s="163"/>
-      <c r="F30" s="163"/>
-      <c r="G30" s="163"/>
+      <c r="B30" s="165"/>
+      <c r="C30" s="165"/>
+      <c r="D30" s="165"/>
+      <c r="E30" s="165"/>
+      <c r="F30" s="165"/>
+      <c r="G30" s="165"/>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D33" s="114"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="I5:K23">
+    <sortCondition descending="1" ref="K5:K23"/>
+  </sortState>
   <mergeCells count="2">
     <mergeCell ref="B30:G30"/>
     <mergeCell ref="B2:G2"/>
@@ -9902,184 +9942,184 @@
   <sheetData>
     <row r="1" spans="2:8" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:8" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="159" t="s">
+      <c r="B2" s="161" t="s">
         <v>249</v>
       </c>
-      <c r="C2" s="160"/>
-      <c r="D2" s="160"/>
-      <c r="E2" s="160"/>
-      <c r="F2" s="160"/>
-      <c r="G2" s="160"/>
-      <c r="H2" s="161"/>
+      <c r="C2" s="162"/>
+      <c r="D2" s="162"/>
+      <c r="E2" s="162"/>
+      <c r="F2" s="162"/>
+      <c r="G2" s="162"/>
+      <c r="H2" s="163"/>
     </row>
     <row r="3" spans="2:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:8" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="164" t="s">
+      <c r="B4" s="166" t="s">
         <v>255</v>
       </c>
-      <c r="C4" s="165"/>
+      <c r="C4" s="167"/>
       <c r="D4" s="43" t="s">
+        <v>294</v>
+      </c>
+      <c r="E4" s="43" t="s">
+        <v>295</v>
+      </c>
+      <c r="F4" s="43" t="s">
         <v>288</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="G4" s="92" t="s">
         <v>289</v>
-      </c>
-      <c r="F4" s="43" t="s">
-        <v>290</v>
-      </c>
-      <c r="G4" s="92" t="s">
-        <v>291</v>
       </c>
       <c r="H4" s="98" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B5" s="166" t="s">
+      <c r="B5" s="168" t="s">
         <v>256</v>
       </c>
       <c r="C5" s="76" t="s">
         <v>257</v>
       </c>
       <c r="D5" s="15">
-        <v>298788</v>
+        <v>380888</v>
       </c>
       <c r="E5" s="16">
-        <v>315129</v>
+        <v>354786</v>
       </c>
       <c r="F5" s="103">
         <f>E5-D5</f>
-        <v>16341</v>
+        <v>-26102</v>
       </c>
       <c r="G5" s="29">
         <f>E5/D5-1</f>
-        <v>5.469095144383318E-2</v>
+        <v>-6.8529331457016229E-2</v>
       </c>
       <c r="H5" s="73">
-        <f>E5/'2026'!D4</f>
-        <v>0.26925771684316474</v>
+        <f>E5/'2026 II კვარტალი'!D4</f>
+        <v>0.22682467448607607</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B6" s="167"/>
+      <c r="B6" s="169"/>
       <c r="C6" s="16" t="s">
         <v>258</v>
       </c>
       <c r="D6" s="15">
-        <v>587958</v>
+        <v>774125</v>
       </c>
       <c r="E6" s="16">
-        <v>567308</v>
+        <v>727585</v>
       </c>
       <c r="F6" s="103">
         <f t="shared" ref="F6:F10" si="0">E6-D6</f>
-        <v>-20650</v>
+        <v>-46540</v>
       </c>
       <c r="G6" s="29">
         <f t="shared" ref="G6:G10" si="1">E6/D6-1</f>
-        <v>-3.51215563016406E-2</v>
+        <v>-6.0119489746487953E-2</v>
       </c>
       <c r="H6" s="73">
-        <f>E6/'2026'!D$4</f>
-        <v>0.48472865660368331</v>
+        <f>E6/'2026 II კვარტალი'!D$4</f>
+        <v>0.46516556680915161</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B7" s="167"/>
+      <c r="B7" s="169"/>
       <c r="C7" s="16" t="s">
         <v>259</v>
       </c>
       <c r="D7" s="15">
-        <v>266245</v>
+        <v>437731</v>
       </c>
       <c r="E7" s="16">
-        <v>269293</v>
+        <v>433111</v>
       </c>
       <c r="F7" s="103">
         <f t="shared" si="0"/>
-        <v>3048</v>
+        <v>-4620</v>
       </c>
       <c r="G7" s="29">
         <f t="shared" si="1"/>
-        <v>1.1448102311780506E-2</v>
+        <v>-1.0554427262405408E-2</v>
       </c>
       <c r="H7" s="73">
-        <f>E7/'2026'!D$4</f>
-        <v>0.23009376586047736</v>
+        <f>E7/'2026 II კვარტალი'!D$4</f>
+        <v>0.27690005127411704</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B8" s="168"/>
+      <c r="B8" s="170"/>
       <c r="C8" s="16" t="s">
         <v>260</v>
       </c>
       <c r="D8" s="15">
-        <v>19345</v>
+        <v>45444</v>
       </c>
       <c r="E8" s="16">
-        <v>18632</v>
+        <v>48660</v>
       </c>
       <c r="F8" s="103">
         <f t="shared" si="0"/>
-        <v>-713</v>
+        <v>3216</v>
       </c>
       <c r="G8" s="29">
         <f t="shared" si="1"/>
-        <v>-3.6857069010080123E-2</v>
+        <v>7.0768418273039257E-2</v>
       </c>
       <c r="H8" s="73">
-        <f>E8/'2026'!D$4</f>
-        <v>1.5919860692674575E-2</v>
+        <f>E8/'2026 II კვარტალი'!D$4</f>
+        <v>3.1109707430655272E-2</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B9" s="169" t="s">
+      <c r="B9" s="171" t="s">
         <v>261</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>262</v>
       </c>
       <c r="D9" s="15">
-        <v>788598</v>
+        <v>1008064</v>
       </c>
       <c r="E9" s="16">
-        <v>765351</v>
+        <v>951104</v>
       </c>
       <c r="F9" s="103">
         <f t="shared" si="0"/>
-        <v>-23247</v>
+        <v>-56960</v>
       </c>
       <c r="G9" s="29">
         <f t="shared" si="1"/>
-        <v>-2.9478897993654551E-2</v>
+        <v>-5.65043489302266E-2</v>
       </c>
       <c r="H9" s="73">
-        <f>E9/'2026'!D$4</f>
-        <v>0.65394382250961669</v>
+        <f>E9/'2026 II კვარტალი'!D$4</f>
+        <v>0.60806755396888523</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="170"/>
+      <c r="B10" s="172"/>
       <c r="C10" s="18" t="s">
         <v>263</v>
       </c>
       <c r="D10" s="69">
-        <v>383738</v>
+        <v>630124</v>
       </c>
       <c r="E10" s="18">
-        <v>405011</v>
+        <v>613038</v>
       </c>
       <c r="F10" s="104">
         <f t="shared" si="0"/>
-        <v>21273</v>
+        <v>-17086</v>
       </c>
       <c r="G10" s="30">
         <f t="shared" si="1"/>
-        <v>5.5436261199047321E-2</v>
+        <v>-2.7115297941357586E-2</v>
       </c>
       <c r="H10" s="74">
-        <f>E10/'2026'!D$4</f>
-        <v>0.34605617749038331</v>
+        <f>E10/'2026 II კვარტალი'!D$4</f>
+        <v>0.39193244603111482</v>
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.2">
